--- a/CSV/ocean ruins.xlsx
+++ b/CSV/ocean ruins.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willem/Documents/GitHub/friend-zone/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willem/Documents/GitHub/friend-zone/CSV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E549EE-D4F5-494C-AEFB-ABFF63342AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5065496-E254-2A49-86CC-59B694AB8232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19120" xr2:uid="{3DA08645-0044-4CD4-8592-6DE51A21B756}"/>
+    <workbookView xWindow="0" yWindow="9580" windowWidth="11480" windowHeight="10040" xr2:uid="{3DA08645-0044-4CD4-8592-6DE51A21B756}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="4">
-  <si>
-    <t>~</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>X</t>
   </si>
@@ -47,7 +47,7 @@
     <t>Z</t>
   </si>
   <si>
-    <t>nummer</t>
+    <t>Ocean Ruins</t>
   </si>
 </sst>
 </file>
@@ -419,7600 +419,5981 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D438CDC-9054-4E83-AD2E-7D63B2C25346}">
-  <dimension ref="A1:D542"/>
+  <dimension ref="A1:C542"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="2.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>5944</v>
       </c>
-      <c r="C2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2">
+      <c r="C2">
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <v>5944</v>
       </c>
-      <c r="C3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3">
+      <c r="C3">
         <v>2312</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
         <v>5944</v>
       </c>
-      <c r="C4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4">
+      <c r="C4">
         <v>4872</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
         <v>5912</v>
       </c>
-      <c r="C5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5">
+      <c r="C5">
         <v>-552</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
         <v>5912</v>
       </c>
-      <c r="C6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6">
+      <c r="C6">
         <v>1976</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
         <v>5912</v>
       </c>
-      <c r="C7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7">
+      <c r="C7">
         <v>1784</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
         <v>5880</v>
       </c>
-      <c r="C8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8">
+      <c r="C8">
         <v>-168</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
         <v>5880</v>
       </c>
-      <c r="C9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9">
+      <c r="C9">
         <v>2600</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
         <v>5864</v>
       </c>
-      <c r="C10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10">
+      <c r="C10">
         <v>1384</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
         <v>5832</v>
       </c>
-      <c r="C11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11">
+      <c r="C11">
         <v>728</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
         <v>5816</v>
       </c>
-      <c r="C12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12">
+      <c r="C12">
         <v>5160</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
         <v>5784</v>
       </c>
-      <c r="C13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13">
+      <c r="C13">
         <v>392</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
         <v>5624</v>
       </c>
-      <c r="C14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14">
+      <c r="C14">
         <v>1288</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
         <v>5624</v>
       </c>
-      <c r="C15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15">
+      <c r="C15">
         <v>5464</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
         <v>5560</v>
       </c>
-      <c r="C16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D16">
+      <c r="C16">
         <v>-520</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
         <v>5560</v>
       </c>
-      <c r="C17" t="s">
-        <v>0</v>
-      </c>
-      <c r="D17">
+      <c r="C17">
         <v>-184</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
         <v>5512</v>
       </c>
-      <c r="C18" t="s">
-        <v>0</v>
-      </c>
-      <c r="D18">
+      <c r="C18">
         <v>2376</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
         <v>5496</v>
       </c>
-      <c r="C19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D19">
+      <c r="C19">
         <v>4984</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
         <v>5480</v>
       </c>
-      <c r="C20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D20">
+      <c r="C20">
         <v>5288</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
         <v>5464</v>
       </c>
-      <c r="C21" t="s">
-        <v>0</v>
-      </c>
-      <c r="D21">
+      <c r="C21">
         <v>-936</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
         <v>5464</v>
       </c>
-      <c r="C22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D22">
+      <c r="C22">
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
         <v>5464</v>
       </c>
-      <c r="C23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D23">
+      <c r="C23">
         <v>1688</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24">
         <v>5464</v>
       </c>
-      <c r="C24" t="s">
-        <v>0</v>
-      </c>
-      <c r="D24">
+      <c r="C24">
         <v>2104</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25">
         <v>5448</v>
       </c>
-      <c r="C25" t="s">
-        <v>0</v>
-      </c>
-      <c r="D25">
+      <c r="C25">
         <v>-1144</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26">
         <v>5448</v>
       </c>
-      <c r="C26" t="s">
-        <v>0</v>
-      </c>
-      <c r="D26">
+      <c r="C26">
         <v>648</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27">
         <v>5304</v>
       </c>
-      <c r="C27" t="s">
-        <v>0</v>
-      </c>
-      <c r="D27">
+      <c r="C27">
         <v>2264</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28">
         <v>5304</v>
       </c>
-      <c r="C28" t="s">
-        <v>0</v>
-      </c>
-      <c r="D28">
+      <c r="C28">
         <v>1640</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29">
         <v>5272</v>
       </c>
-      <c r="C29" t="s">
-        <v>0</v>
-      </c>
-      <c r="D29">
+      <c r="C29">
         <v>1464</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30">
         <v>5256</v>
       </c>
-      <c r="C30" t="s">
-        <v>0</v>
-      </c>
-      <c r="D30">
+      <c r="C30">
         <v>-920</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31">
         <v>5256</v>
       </c>
-      <c r="C31" t="s">
-        <v>0</v>
-      </c>
-      <c r="D31">
+      <c r="C31">
         <v>-280</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32">
         <v>5256</v>
       </c>
-      <c r="C32" t="s">
-        <v>0</v>
-      </c>
-      <c r="D32">
+      <c r="C32">
         <v>1960</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33">
         <v>5176</v>
       </c>
-      <c r="C33" t="s">
-        <v>0</v>
-      </c>
-      <c r="D33">
+      <c r="C33">
         <v>712</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34">
         <v>5144</v>
       </c>
-      <c r="C34" t="s">
-        <v>0</v>
-      </c>
-      <c r="D34">
+      <c r="C34">
         <v>-552</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35">
         <v>4968</v>
       </c>
-      <c r="C35" t="s">
-        <v>0</v>
-      </c>
-      <c r="D35">
+      <c r="C35">
         <v>2296</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36">
         <v>4968</v>
       </c>
-      <c r="C36" t="s">
-        <v>0</v>
-      </c>
-      <c r="D36">
+      <c r="C36">
         <v>1704</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37">
         <v>4968</v>
       </c>
-      <c r="C37" t="s">
-        <v>0</v>
-      </c>
-      <c r="D37">
+      <c r="C37">
         <v>2040</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38">
         <v>4920</v>
       </c>
-      <c r="C38" t="s">
-        <v>0</v>
-      </c>
-      <c r="D38">
+      <c r="C38">
         <v>-792</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39">
         <v>4824</v>
       </c>
-      <c r="C39" t="s">
-        <v>0</v>
-      </c>
-      <c r="D39">
+      <c r="C39">
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40">
         <v>4648</v>
       </c>
-      <c r="C40" t="s">
-        <v>0</v>
-      </c>
-      <c r="D40">
+      <c r="C40">
         <v>2104</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41">
         <v>4648</v>
       </c>
-      <c r="C41" t="s">
-        <v>0</v>
-      </c>
-      <c r="D41">
+      <c r="C41">
         <v>1736</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42">
         <v>4632</v>
       </c>
-      <c r="C42" t="s">
-        <v>0</v>
-      </c>
-      <c r="D42">
+      <c r="C42">
         <v>3368</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43">
         <v>4616</v>
       </c>
-      <c r="C43" t="s">
-        <v>0</v>
-      </c>
-      <c r="D43">
+      <c r="C43">
         <v>1368</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44">
         <v>4504</v>
       </c>
-      <c r="C44" t="s">
-        <v>0</v>
-      </c>
-      <c r="D44">
+      <c r="C44">
         <v>5176</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45">
         <v>4344</v>
       </c>
-      <c r="C45" t="s">
-        <v>0</v>
-      </c>
-      <c r="D45">
+      <c r="C45">
         <v>2008</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46">
         <v>4312</v>
       </c>
-      <c r="C46" t="s">
-        <v>0</v>
-      </c>
-      <c r="D46">
+      <c r="C46">
         <v>5240</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47">
         <v>4280</v>
       </c>
-      <c r="C47" t="s">
-        <v>0</v>
-      </c>
-      <c r="D47">
+      <c r="C47">
         <v>1640</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48">
         <v>3992</v>
       </c>
-      <c r="C48" t="s">
-        <v>0</v>
-      </c>
-      <c r="D48">
+      <c r="C48">
         <v>2376</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49">
         <v>3976</v>
       </c>
-      <c r="C49" t="s">
-        <v>0</v>
-      </c>
-      <c r="D49">
+      <c r="C49">
         <v>3672</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50">
         <v>3960</v>
       </c>
-      <c r="C50" t="s">
-        <v>0</v>
-      </c>
-      <c r="D50">
+      <c r="C50">
         <v>1752</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51">
         <v>3960</v>
       </c>
-      <c r="C51" t="s">
-        <v>0</v>
-      </c>
-      <c r="D51">
+      <c r="C51">
         <v>2712</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52">
         <v>3960</v>
       </c>
-      <c r="C52" t="s">
-        <v>0</v>
-      </c>
-      <c r="D52">
+      <c r="C52">
         <v>5144</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53">
         <v>3928</v>
       </c>
-      <c r="C53" t="s">
-        <v>0</v>
-      </c>
-      <c r="D53">
+      <c r="C53">
         <v>3048</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54">
         <v>3896</v>
       </c>
-      <c r="C54" t="s">
-        <v>0</v>
-      </c>
-      <c r="D54">
+      <c r="C54">
         <v>1960</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55">
         <v>3896</v>
       </c>
-      <c r="C55" t="s">
-        <v>0</v>
-      </c>
-      <c r="D55">
+      <c r="C55">
         <v>3288</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56">
         <v>3896</v>
       </c>
-      <c r="C56" t="s">
-        <v>0</v>
-      </c>
-      <c r="D56">
+      <c r="C56">
         <v>5512</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57">
         <v>3880</v>
       </c>
-      <c r="C57" t="s">
-        <v>0</v>
-      </c>
-      <c r="D57">
+      <c r="C57">
         <v>-5400</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58">
         <v>3848</v>
       </c>
-      <c r="C58" t="s">
-        <v>0</v>
-      </c>
-      <c r="D58">
+      <c r="C58">
         <v>-4952</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59">
         <v>3672</v>
       </c>
-      <c r="C59" t="s">
-        <v>0</v>
-      </c>
-      <c r="D59">
+      <c r="C59">
         <v>-5336</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60">
         <v>3672</v>
       </c>
-      <c r="C60" t="s">
-        <v>0</v>
-      </c>
-      <c r="D60">
+      <c r="C60">
         <v>-4936</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61">
         <v>3672</v>
       </c>
-      <c r="C61" t="s">
-        <v>0</v>
-      </c>
-      <c r="D61">
+      <c r="C61">
         <v>5160</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62">
         <v>3656</v>
       </c>
-      <c r="C62" t="s">
-        <v>0</v>
-      </c>
-      <c r="D62">
+      <c r="C62">
         <v>3000</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63">
         <v>3640</v>
       </c>
-      <c r="C63" t="s">
-        <v>0</v>
-      </c>
-      <c r="D63">
+      <c r="C63">
         <v>-5576</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64">
         <v>3624</v>
       </c>
-      <c r="C64" t="s">
-        <v>0</v>
-      </c>
-      <c r="D64">
+      <c r="C64">
         <v>-4456</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65">
         <v>3624</v>
       </c>
-      <c r="C65" t="s">
-        <v>0</v>
-      </c>
-      <c r="D65">
+      <c r="C65">
         <v>2696</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66">
         <v>3624</v>
       </c>
-      <c r="C66" t="s">
-        <v>0</v>
-      </c>
-      <c r="D66">
+      <c r="C66">
         <v>3608</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67">
         <v>3608</v>
       </c>
-      <c r="C67" t="s">
-        <v>0</v>
-      </c>
-      <c r="D67">
+      <c r="C67">
         <v>1304</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68">
         <v>3608</v>
       </c>
-      <c r="C68" t="s">
-        <v>0</v>
-      </c>
-      <c r="D68">
+      <c r="C68">
         <v>1752</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69">
         <v>3608</v>
       </c>
-      <c r="C69" t="s">
-        <v>0</v>
-      </c>
-      <c r="D69">
+      <c r="C69">
         <v>4856</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70">
         <v>3576</v>
       </c>
-      <c r="C70" t="s">
-        <v>0</v>
-      </c>
-      <c r="D70">
+      <c r="C70">
         <v>-4680</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71">
         <v>3576</v>
       </c>
-      <c r="C71" t="s">
-        <v>0</v>
-      </c>
-      <c r="D71">
+      <c r="C71">
         <v>2376</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72">
         <v>3560</v>
       </c>
-      <c r="C72" t="s">
-        <v>0</v>
-      </c>
-      <c r="D72">
+      <c r="C72">
         <v>3336</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73">
         <v>3560</v>
       </c>
-      <c r="C73" t="s">
-        <v>0</v>
-      </c>
-      <c r="D73">
+      <c r="C73">
         <v>5624</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74">
         <v>3528</v>
       </c>
-      <c r="C74" t="s">
-        <v>0</v>
-      </c>
-      <c r="D74">
+      <c r="C74">
         <v>-2808</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75">
         <v>3528</v>
       </c>
-      <c r="C75" t="s">
-        <v>0</v>
-      </c>
-      <c r="D75">
+      <c r="C75">
         <v>1080</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76">
         <v>3528</v>
       </c>
-      <c r="C76" t="s">
-        <v>0</v>
-      </c>
-      <c r="D76">
+      <c r="C76">
         <v>2072</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77">
         <v>3384</v>
       </c>
-      <c r="C77" t="s">
-        <v>0</v>
-      </c>
-      <c r="D77">
+      <c r="C77">
         <v>5768</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78">
         <v>3384</v>
       </c>
-      <c r="C78" t="s">
-        <v>0</v>
-      </c>
-      <c r="D78">
+      <c r="C78">
         <v>5128</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79">
         <v>3368</v>
       </c>
-      <c r="C79" t="s">
-        <v>0</v>
-      </c>
-      <c r="D79">
+      <c r="C79">
         <v>-4136</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80">
         <v>3352</v>
       </c>
-      <c r="C80" t="s">
-        <v>0</v>
-      </c>
-      <c r="D80">
+      <c r="C80">
         <v>-4696</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81">
         <v>3352</v>
       </c>
-      <c r="C81" t="s">
-        <v>0</v>
-      </c>
-      <c r="D81">
+      <c r="C81">
         <v>-2200</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82">
         <v>3352</v>
       </c>
-      <c r="C82" t="s">
-        <v>0</v>
-      </c>
-      <c r="D82">
+      <c r="C82">
         <v>3224</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83">
         <v>3336</v>
       </c>
-      <c r="C83" t="s">
-        <v>0</v>
-      </c>
-      <c r="D83">
+      <c r="C83">
         <v>2280</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84">
         <v>3336</v>
       </c>
-      <c r="C84" t="s">
-        <v>0</v>
-      </c>
-      <c r="D84">
+      <c r="C84">
         <v>3000</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85">
         <v>3336</v>
       </c>
-      <c r="C85" t="s">
-        <v>0</v>
-      </c>
-      <c r="D85">
+      <c r="C85">
         <v>3960</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86">
         <v>3320</v>
       </c>
-      <c r="C86" t="s">
-        <v>0</v>
-      </c>
-      <c r="D86">
+      <c r="C86">
         <v>-5096</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87">
         <v>3304</v>
       </c>
-      <c r="C87" t="s">
-        <v>0</v>
-      </c>
-      <c r="D87">
+      <c r="C87">
         <v>1448</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88">
         <v>3304</v>
       </c>
-      <c r="C88" t="s">
-        <v>0</v>
-      </c>
-      <c r="D88">
+      <c r="C88">
         <v>1608</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89">
         <v>3304</v>
       </c>
-      <c r="C89" t="s">
-        <v>0</v>
-      </c>
-      <c r="D89">
+      <c r="C89">
         <v>5480</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90">
         <v>3224</v>
       </c>
-      <c r="C90" t="s">
-        <v>0</v>
-      </c>
-      <c r="D90">
+      <c r="C90">
         <v>-5288</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91">
         <v>3224</v>
       </c>
-      <c r="C91" t="s">
-        <v>0</v>
-      </c>
-      <c r="D91">
+      <c r="C91">
         <v>-2760</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92">
         <v>3224</v>
       </c>
-      <c r="C92" t="s">
-        <v>0</v>
-      </c>
-      <c r="D92">
+      <c r="C92">
         <v>1976</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93">
         <v>3208</v>
       </c>
-      <c r="C93" t="s">
-        <v>0</v>
-      </c>
-      <c r="D93">
+      <c r="C93">
         <v>-4360</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94">
         <v>3208</v>
       </c>
-      <c r="C94" t="s">
-        <v>0</v>
-      </c>
-      <c r="D94">
+      <c r="C94">
         <v>-2552</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95">
         <v>3064</v>
       </c>
-      <c r="C95" t="s">
-        <v>0</v>
-      </c>
-      <c r="D95">
+      <c r="C95">
         <v>-1480</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96">
         <v>3064</v>
       </c>
-      <c r="C96" t="s">
-        <v>0</v>
-      </c>
-      <c r="D96">
+      <c r="C96">
         <v>1368</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97">
         <v>3048</v>
       </c>
-      <c r="C97" t="s">
-        <v>0</v>
-      </c>
-      <c r="D97">
+      <c r="C97">
         <v>2328</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98">
         <v>3032</v>
       </c>
-      <c r="C98" t="s">
-        <v>0</v>
-      </c>
-      <c r="D98">
+      <c r="C98">
         <v>5160</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99">
         <v>3016</v>
       </c>
-      <c r="C99" t="s">
-        <v>0</v>
-      </c>
-      <c r="D99">
+      <c r="C99">
         <v>1976</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>99</v>
       </c>
       <c r="B100">
         <v>3000</v>
       </c>
-      <c r="C100" t="s">
-        <v>0</v>
-      </c>
-      <c r="D100">
+      <c r="C100">
         <v>-1880</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101">
         <v>3000</v>
       </c>
-      <c r="C101" t="s">
-        <v>0</v>
-      </c>
-      <c r="D101">
+      <c r="C101">
         <v>3048</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>101</v>
       </c>
       <c r="B102">
         <v>3000</v>
       </c>
-      <c r="C102" t="s">
-        <v>0</v>
-      </c>
-      <c r="D102">
+      <c r="C102">
         <v>3384</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>102</v>
       </c>
       <c r="B103">
         <v>2984</v>
       </c>
-      <c r="C103" t="s">
-        <v>0</v>
-      </c>
-      <c r="D103">
+      <c r="C103">
         <v>2728</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>103</v>
       </c>
       <c r="B104">
         <v>2984</v>
       </c>
-      <c r="C104" t="s">
-        <v>0</v>
-      </c>
-      <c r="D104">
+      <c r="C104">
         <v>4968</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>104</v>
       </c>
       <c r="B105">
         <v>2968</v>
       </c>
-      <c r="C105" t="s">
-        <v>0</v>
-      </c>
-      <c r="D105">
+      <c r="C105">
         <v>4008</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>105</v>
       </c>
       <c r="B106">
         <v>2952</v>
       </c>
-      <c r="C106" t="s">
-        <v>0</v>
-      </c>
-      <c r="D106">
+      <c r="C106">
         <v>-4760</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>106</v>
       </c>
       <c r="B107">
         <v>2952</v>
       </c>
-      <c r="C107" t="s">
-        <v>0</v>
-      </c>
-      <c r="D107">
+      <c r="C107">
         <v>-2216</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>107</v>
       </c>
       <c r="B108">
         <v>2936</v>
       </c>
-      <c r="C108" t="s">
-        <v>0</v>
-      </c>
-      <c r="D108">
+      <c r="C108">
         <v>1672</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>108</v>
       </c>
       <c r="B109">
         <v>2936</v>
       </c>
-      <c r="C109" t="s">
-        <v>0</v>
-      </c>
-      <c r="D109">
+      <c r="C109">
         <v>5880</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>109</v>
       </c>
       <c r="B110">
         <v>2920</v>
       </c>
-      <c r="C110" t="s">
-        <v>0</v>
-      </c>
-      <c r="D110">
+      <c r="C110">
         <v>-5064</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>110</v>
       </c>
       <c r="B111">
         <v>2920</v>
       </c>
-      <c r="C111" t="s">
-        <v>0</v>
-      </c>
-      <c r="D111">
+      <c r="C111">
         <v>5512</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>111</v>
       </c>
       <c r="B112">
         <v>2904</v>
       </c>
-      <c r="C112" t="s">
-        <v>0</v>
-      </c>
-      <c r="D112">
+      <c r="C112">
         <v>-2504</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>112</v>
       </c>
       <c r="B113">
         <v>2744</v>
       </c>
-      <c r="C113" t="s">
-        <v>0</v>
-      </c>
-      <c r="D113">
+      <c r="C113">
         <v>3352</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>113</v>
       </c>
       <c r="B114">
         <v>2744</v>
       </c>
-      <c r="C114" t="s">
-        <v>0</v>
-      </c>
-      <c r="D114">
+      <c r="C114">
         <v>2376</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>114</v>
       </c>
       <c r="B115">
         <v>2728</v>
       </c>
-      <c r="C115" t="s">
-        <v>0</v>
-      </c>
-      <c r="D115">
+      <c r="C115">
         <v>-5112</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>115</v>
       </c>
       <c r="B116">
         <v>2728</v>
       </c>
-      <c r="C116" t="s">
-        <v>0</v>
-      </c>
-      <c r="D116">
+      <c r="C116">
         <v>2744</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>116</v>
       </c>
       <c r="B117">
         <v>2728</v>
       </c>
-      <c r="C117" t="s">
-        <v>0</v>
-      </c>
-      <c r="D117">
+      <c r="C117">
         <v>2904</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>117</v>
       </c>
       <c r="B118">
         <v>2728</v>
       </c>
-      <c r="C118" t="s">
-        <v>0</v>
-      </c>
-      <c r="D118">
+      <c r="C118">
         <v>3960</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>118</v>
       </c>
       <c r="B119">
         <v>2664</v>
       </c>
-      <c r="C119" t="s">
-        <v>0</v>
-      </c>
-      <c r="D119">
+      <c r="C119">
         <v>1688</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>119</v>
       </c>
       <c r="B120">
         <v>2648</v>
       </c>
-      <c r="C120" t="s">
-        <v>0</v>
-      </c>
-      <c r="D120">
+      <c r="C120">
         <v>5464</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>120</v>
       </c>
       <c r="B121">
         <v>2648</v>
       </c>
-      <c r="C121" t="s">
-        <v>0</v>
-      </c>
-      <c r="D121">
+      <c r="C121">
         <v>5912</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>121</v>
       </c>
       <c r="B122">
         <v>2632</v>
       </c>
-      <c r="C122" t="s">
-        <v>0</v>
-      </c>
-      <c r="D122">
+      <c r="C122">
         <v>-5304</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>122</v>
       </c>
       <c r="B123">
         <v>2632</v>
       </c>
-      <c r="C123" t="s">
-        <v>0</v>
-      </c>
-      <c r="D123">
+      <c r="C123">
         <v>1976</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>123</v>
       </c>
       <c r="B124">
         <v>2632</v>
       </c>
-      <c r="C124" t="s">
-        <v>0</v>
-      </c>
-      <c r="D124">
+      <c r="C124">
         <v>3704</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>124</v>
       </c>
       <c r="B125">
         <v>2616</v>
       </c>
-      <c r="C125" t="s">
-        <v>0</v>
-      </c>
-      <c r="D125">
+      <c r="C125">
         <v>-4632</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>125</v>
       </c>
       <c r="B126">
         <v>2616</v>
       </c>
-      <c r="C126" t="s">
-        <v>0</v>
-      </c>
-      <c r="D126">
+      <c r="C126">
         <v>-1576</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>126</v>
       </c>
       <c r="B127">
         <v>2616</v>
       </c>
-      <c r="C127" t="s">
-        <v>0</v>
-      </c>
-      <c r="D127">
+      <c r="C127">
         <v>-2056</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>127</v>
       </c>
       <c r="B128">
         <v>2600</v>
       </c>
-      <c r="C128" t="s">
-        <v>0</v>
-      </c>
-      <c r="D128">
+      <c r="C128">
         <v>-1848</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>128</v>
       </c>
       <c r="B129">
         <v>2584</v>
       </c>
-      <c r="C129" t="s">
-        <v>0</v>
-      </c>
-      <c r="D129">
+      <c r="C129">
         <v>1352</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>129</v>
       </c>
       <c r="B130">
         <v>2584</v>
       </c>
-      <c r="C130" t="s">
-        <v>0</v>
-      </c>
-      <c r="D130">
+      <c r="C130">
         <v>4824</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>130</v>
       </c>
       <c r="B131">
         <v>2568</v>
       </c>
-      <c r="C131" t="s">
-        <v>0</v>
-      </c>
-      <c r="D131">
+      <c r="C131">
         <v>5240</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>131</v>
       </c>
       <c r="B132">
         <v>2424</v>
       </c>
-      <c r="C132" t="s">
-        <v>0</v>
-      </c>
-      <c r="D132">
+      <c r="C132">
         <v>-216</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>132</v>
       </c>
       <c r="B133">
         <v>2424</v>
       </c>
-      <c r="C133" t="s">
-        <v>0</v>
-      </c>
-      <c r="D133">
+      <c r="C133">
         <v>1432</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>133</v>
       </c>
       <c r="B134">
         <v>2424</v>
       </c>
-      <c r="C134" t="s">
-        <v>0</v>
-      </c>
-      <c r="D134">
+      <c r="C134">
         <v>3048</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>134</v>
       </c>
       <c r="B135">
         <v>2424</v>
       </c>
-      <c r="C135" t="s">
-        <v>0</v>
-      </c>
-      <c r="D135">
+      <c r="C135">
         <v>4984</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>135</v>
       </c>
       <c r="B136">
         <v>2408</v>
       </c>
-      <c r="C136" t="s">
-        <v>0</v>
-      </c>
-      <c r="D136">
+      <c r="C136">
         <v>-2392</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>136</v>
       </c>
       <c r="B137">
         <v>2408</v>
       </c>
-      <c r="C137" t="s">
-        <v>0</v>
-      </c>
-      <c r="D137">
+      <c r="C137">
         <v>-2184</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>137</v>
       </c>
       <c r="B138">
         <v>2408</v>
       </c>
-      <c r="C138" t="s">
-        <v>0</v>
-      </c>
-      <c r="D138">
+      <c r="C138">
         <v>-1912</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>138</v>
       </c>
       <c r="B139">
         <v>2392</v>
       </c>
-      <c r="C139" t="s">
-        <v>0</v>
-      </c>
-      <c r="D139">
+      <c r="C139">
         <v>1688</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>139</v>
       </c>
       <c r="B140">
         <v>2376</v>
       </c>
-      <c r="C140" t="s">
-        <v>0</v>
-      </c>
-      <c r="D140">
+      <c r="C140">
         <v>-5704</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>140</v>
       </c>
       <c r="B141">
         <v>2376</v>
       </c>
-      <c r="C141" t="s">
-        <v>0</v>
-      </c>
-      <c r="D141">
+      <c r="C141">
         <v>2392</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>141</v>
       </c>
       <c r="B142">
         <v>2344</v>
       </c>
-      <c r="C142" t="s">
-        <v>0</v>
-      </c>
-      <c r="D142">
+      <c r="C142">
         <v>-584</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>142</v>
       </c>
       <c r="B143">
         <v>2344</v>
       </c>
-      <c r="C143" t="s">
-        <v>0</v>
-      </c>
-      <c r="D143">
+      <c r="C143">
         <v>3640</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>143</v>
       </c>
       <c r="B144">
         <v>2344</v>
       </c>
-      <c r="C144" t="s">
-        <v>0</v>
-      </c>
-      <c r="D144">
+      <c r="C144">
         <v>5272</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>144</v>
       </c>
       <c r="B145">
         <v>2328</v>
       </c>
-      <c r="C145" t="s">
-        <v>0</v>
-      </c>
-      <c r="D145">
+      <c r="C145">
         <v>1128</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>145</v>
       </c>
       <c r="B146">
         <v>2312</v>
       </c>
-      <c r="C146" t="s">
-        <v>0</v>
-      </c>
-      <c r="D146">
+      <c r="C146">
         <v>-4776</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>146</v>
       </c>
       <c r="B147">
         <v>2312</v>
       </c>
-      <c r="C147" t="s">
-        <v>0</v>
-      </c>
-      <c r="D147">
+      <c r="C147">
         <v>2616</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>147</v>
       </c>
       <c r="B148">
         <v>2312</v>
       </c>
-      <c r="C148" t="s">
-        <v>0</v>
-      </c>
-      <c r="D148">
+      <c r="C148">
         <v>5448</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>148</v>
       </c>
       <c r="B149">
         <v>2296</v>
       </c>
-      <c r="C149" t="s">
-        <v>0</v>
-      </c>
-      <c r="D149">
+      <c r="C149">
         <v>-1208</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>149</v>
       </c>
       <c r="B150">
         <v>2280</v>
       </c>
-      <c r="C150" t="s">
-        <v>0</v>
-      </c>
-      <c r="D150">
+      <c r="C150">
         <v>4584</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>150</v>
       </c>
       <c r="B151">
         <v>2280</v>
       </c>
-      <c r="C151" t="s">
-        <v>0</v>
-      </c>
-      <c r="D151">
+      <c r="C151">
         <v>5800</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>151</v>
       </c>
       <c r="B152">
         <v>2264</v>
       </c>
-      <c r="C152" t="s">
-        <v>0</v>
-      </c>
-      <c r="D152">
+      <c r="C152">
         <v>3352</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>152</v>
       </c>
       <c r="B153">
         <v>2264</v>
       </c>
-      <c r="C153" t="s">
-        <v>0</v>
-      </c>
-      <c r="D153">
+      <c r="C153">
         <v>2056</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>153</v>
       </c>
       <c r="B154">
         <v>2104</v>
       </c>
-      <c r="C154" t="s">
-        <v>0</v>
-      </c>
-      <c r="D154">
+      <c r="C154">
         <v>1128</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>154</v>
       </c>
       <c r="B155">
         <v>2104</v>
       </c>
-      <c r="C155" t="s">
-        <v>0</v>
-      </c>
-      <c r="D155">
+      <c r="C155">
         <v>4296</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>155</v>
       </c>
       <c r="B156">
         <v>2104</v>
       </c>
-      <c r="C156" t="s">
-        <v>0</v>
-      </c>
-      <c r="D156">
+      <c r="C156">
         <v>4536</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>156</v>
       </c>
       <c r="B157">
         <v>2072</v>
       </c>
-      <c r="C157" t="s">
-        <v>0</v>
-      </c>
-      <c r="D157">
+      <c r="C157">
         <v>-184</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>157</v>
       </c>
       <c r="B158">
         <v>2072</v>
       </c>
-      <c r="C158" t="s">
-        <v>0</v>
-      </c>
-      <c r="D158">
+      <c r="C158">
         <v>2424</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>158</v>
       </c>
       <c r="B159">
         <v>2056</v>
       </c>
-      <c r="C159" t="s">
-        <v>0</v>
-      </c>
-      <c r="D159">
+      <c r="C159">
         <v>-1256</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>159</v>
       </c>
       <c r="B160">
         <v>2056</v>
       </c>
-      <c r="C160" t="s">
-        <v>0</v>
-      </c>
-      <c r="D160">
+      <c r="C160">
         <v>3000</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>160</v>
       </c>
       <c r="B161">
         <v>2040</v>
       </c>
-      <c r="C161" t="s">
-        <v>0</v>
-      </c>
-      <c r="D161">
+      <c r="C161">
         <v>5768</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>161</v>
       </c>
       <c r="B162">
         <v>2024</v>
       </c>
-      <c r="C162" t="s">
-        <v>0</v>
-      </c>
-      <c r="D162">
+      <c r="C162">
         <v>-456</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>162</v>
       </c>
       <c r="B163">
         <v>2024</v>
       </c>
-      <c r="C163" t="s">
-        <v>0</v>
-      </c>
-      <c r="D163">
+      <c r="C163">
         <v>3624</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>163</v>
       </c>
       <c r="B164">
         <v>2024</v>
       </c>
-      <c r="C164" t="s">
-        <v>0</v>
-      </c>
-      <c r="D164">
+      <c r="C164">
         <v>5160</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>164</v>
       </c>
       <c r="B165">
         <v>2008</v>
       </c>
-      <c r="C165" t="s">
-        <v>0</v>
-      </c>
-      <c r="D165">
+      <c r="C165">
         <v>-2104</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>165</v>
       </c>
       <c r="B166">
         <v>2008</v>
       </c>
-      <c r="C166" t="s">
-        <v>0</v>
-      </c>
-      <c r="D166">
+      <c r="C166">
         <v>2744</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>166</v>
       </c>
       <c r="B167">
         <v>2008</v>
       </c>
-      <c r="C167" t="s">
-        <v>0</v>
-      </c>
-      <c r="D167">
+      <c r="C167">
         <v>2088</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>167</v>
       </c>
       <c r="B168">
         <v>2008</v>
       </c>
-      <c r="C168" t="s">
-        <v>0</v>
-      </c>
-      <c r="D168">
+      <c r="C168">
         <v>4984</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>168</v>
       </c>
       <c r="B169">
         <v>2008</v>
       </c>
-      <c r="C169" t="s">
-        <v>0</v>
-      </c>
-      <c r="D169">
+      <c r="C169">
         <v>5608</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>169</v>
       </c>
       <c r="B170">
         <v>1992</v>
       </c>
-      <c r="C170" t="s">
-        <v>0</v>
-      </c>
-      <c r="D170">
+      <c r="C170">
         <v>728</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>170</v>
       </c>
       <c r="B171">
         <v>1992</v>
       </c>
-      <c r="C171" t="s">
-        <v>0</v>
-      </c>
-      <c r="D171">
+      <c r="C171">
         <v>3864</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>171</v>
       </c>
       <c r="B172">
         <v>1976</v>
       </c>
-      <c r="C172" t="s">
-        <v>0</v>
-      </c>
-      <c r="D172">
+      <c r="C172">
         <v>-1432</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>172</v>
       </c>
       <c r="B173">
         <v>1960</v>
       </c>
-      <c r="C173" t="s">
-        <v>0</v>
-      </c>
-      <c r="D173">
+      <c r="C173">
         <v>-920</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>173</v>
       </c>
       <c r="B174">
         <v>1960</v>
       </c>
-      <c r="C174" t="s">
-        <v>0</v>
-      </c>
-      <c r="D174">
+      <c r="C174">
         <v>1656</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>174</v>
       </c>
       <c r="B175">
         <v>1960</v>
       </c>
-      <c r="C175" t="s">
-        <v>0</v>
-      </c>
-      <c r="D175">
+      <c r="C175">
         <v>3256</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>175</v>
       </c>
       <c r="B176">
         <v>1944</v>
       </c>
-      <c r="C176" t="s">
-        <v>0</v>
-      </c>
-      <c r="D176">
+      <c r="C176">
         <v>1416</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>176</v>
       </c>
       <c r="B177">
         <v>1928</v>
       </c>
-      <c r="C177" t="s">
-        <v>0</v>
-      </c>
-      <c r="D177">
+      <c r="C177">
         <v>-2472</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>177</v>
       </c>
       <c r="B178">
         <v>1784</v>
       </c>
-      <c r="C178" t="s">
-        <v>0</v>
-      </c>
-      <c r="D178">
+      <c r="C178">
         <v>1752</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>178</v>
       </c>
       <c r="B179">
         <v>1784</v>
       </c>
-      <c r="C179" t="s">
-        <v>0</v>
-      </c>
-      <c r="D179">
+      <c r="C179">
         <v>5784</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>179</v>
       </c>
       <c r="B180">
         <v>1768</v>
       </c>
-      <c r="C180" t="s">
-        <v>0</v>
-      </c>
-      <c r="D180">
+      <c r="C180">
         <v>-136</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>180</v>
       </c>
       <c r="B181">
         <v>1736</v>
       </c>
-      <c r="C181" t="s">
-        <v>0</v>
-      </c>
-      <c r="D181">
+      <c r="C181">
         <v>-488</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>181</v>
       </c>
       <c r="B182">
         <v>1736</v>
       </c>
-      <c r="C182" t="s">
-        <v>0</v>
-      </c>
-      <c r="D182">
+      <c r="C182">
         <v>408</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>182</v>
       </c>
       <c r="B183">
         <v>1720</v>
       </c>
-      <c r="C183" t="s">
-        <v>0</v>
-      </c>
-      <c r="D183">
+      <c r="C183">
         <v>-2216</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>183</v>
       </c>
       <c r="B184">
         <v>1720</v>
       </c>
-      <c r="C184" t="s">
-        <v>0</v>
-      </c>
-      <c r="D184">
+      <c r="C184">
         <v>3272</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>184</v>
       </c>
       <c r="B185">
         <v>1720</v>
       </c>
-      <c r="C185" t="s">
-        <v>0</v>
-      </c>
-      <c r="D185">
+      <c r="C185">
         <v>2024</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>185</v>
       </c>
       <c r="B186">
         <v>1720</v>
       </c>
-      <c r="C186" t="s">
-        <v>0</v>
-      </c>
-      <c r="D186">
+      <c r="C186">
         <v>4264</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>186</v>
       </c>
       <c r="B187">
         <v>1704</v>
       </c>
-      <c r="C187" t="s">
-        <v>0</v>
-      </c>
-      <c r="D187">
+      <c r="C187">
         <v>-2376</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>187</v>
       </c>
       <c r="B188">
         <v>1704</v>
       </c>
-      <c r="C188" t="s">
-        <v>0</v>
-      </c>
-      <c r="D188">
+      <c r="C188">
         <v>1144</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>188</v>
       </c>
       <c r="B189">
         <v>1704</v>
       </c>
-      <c r="C189" t="s">
-        <v>0</v>
-      </c>
-      <c r="D189">
+      <c r="C189">
         <v>3672</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>189</v>
       </c>
       <c r="B190">
         <v>1688</v>
       </c>
-      <c r="C190" t="s">
-        <v>0</v>
-      </c>
-      <c r="D190">
+      <c r="C190">
         <v>-2856</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>190</v>
       </c>
       <c r="B191">
         <v>1688</v>
       </c>
-      <c r="C191" t="s">
-        <v>0</v>
-      </c>
-      <c r="D191">
+      <c r="C191">
         <v>4616</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>191</v>
       </c>
       <c r="B192">
         <v>1672</v>
       </c>
-      <c r="C192" t="s">
-        <v>0</v>
-      </c>
-      <c r="D192">
+      <c r="C192">
         <v>-3016</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>192</v>
       </c>
       <c r="B193">
         <v>1672</v>
       </c>
-      <c r="C193" t="s">
-        <v>0</v>
-      </c>
-      <c r="D193">
+      <c r="C193">
         <v>2680</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>193</v>
       </c>
       <c r="B194">
         <v>1672</v>
       </c>
-      <c r="C194" t="s">
-        <v>0</v>
-      </c>
-      <c r="D194">
+      <c r="C194">
         <v>2248</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>194</v>
       </c>
       <c r="B195">
         <v>1672</v>
       </c>
-      <c r="C195" t="s">
-        <v>0</v>
-      </c>
-      <c r="D195">
+      <c r="C195">
         <v>4808</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>195</v>
       </c>
       <c r="B196">
         <v>1656</v>
       </c>
-      <c r="C196" t="s">
-        <v>0</v>
-      </c>
-      <c r="D196">
+      <c r="C196">
         <v>-792</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>196</v>
       </c>
       <c r="B197">
         <v>1656</v>
       </c>
-      <c r="C197" t="s">
-        <v>0</v>
-      </c>
-      <c r="D197">
+      <c r="C197">
         <v>-1128</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>197</v>
       </c>
       <c r="B198">
         <v>1624</v>
       </c>
-      <c r="C198" t="s">
-        <v>0</v>
-      </c>
-      <c r="D198">
+      <c r="C198">
         <v>-1432</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>198</v>
       </c>
       <c r="B199">
         <v>1624</v>
       </c>
-      <c r="C199" t="s">
-        <v>0</v>
-      </c>
-      <c r="D199">
+      <c r="C199">
         <v>120</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>199</v>
       </c>
       <c r="B200">
         <v>1624</v>
       </c>
-      <c r="C200" t="s">
-        <v>0</v>
-      </c>
-      <c r="D200">
+      <c r="C200">
         <v>5144</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>200</v>
       </c>
       <c r="B201">
         <v>1608</v>
       </c>
-      <c r="C201" t="s">
-        <v>0</v>
-      </c>
-      <c r="D201">
+      <c r="C201">
         <v>-1880</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>201</v>
       </c>
       <c r="B202">
         <v>1608</v>
       </c>
-      <c r="C202" t="s">
-        <v>0</v>
-      </c>
-      <c r="D202">
+      <c r="C202">
         <v>808</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>202</v>
       </c>
       <c r="B203">
         <v>1608</v>
       </c>
-      <c r="C203" t="s">
-        <v>0</v>
-      </c>
-      <c r="D203">
+      <c r="C203">
         <v>3896</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>203</v>
       </c>
       <c r="B204">
         <v>1608</v>
       </c>
-      <c r="C204" t="s">
-        <v>0</v>
-      </c>
-      <c r="D204">
+      <c r="C204">
         <v>5496</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>204</v>
       </c>
       <c r="B205">
         <v>1448</v>
       </c>
-      <c r="C205" t="s">
-        <v>0</v>
-      </c>
-      <c r="D205">
+      <c r="C205">
         <v>-2440</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>205</v>
       </c>
       <c r="B206">
         <v>1448</v>
       </c>
-      <c r="C206" t="s">
-        <v>0</v>
-      </c>
-      <c r="D206">
+      <c r="C206">
         <v>-2232</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>206</v>
       </c>
       <c r="B207">
         <v>1448</v>
       </c>
-      <c r="C207" t="s">
-        <v>0</v>
-      </c>
-      <c r="D207">
+      <c r="C207">
         <v>5128</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>207</v>
       </c>
       <c r="B208">
         <v>1432</v>
       </c>
-      <c r="C208" t="s">
-        <v>0</v>
-      </c>
-      <c r="D208">
+      <c r="C208">
         <v>5832</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>208</v>
       </c>
       <c r="B209">
         <v>1416</v>
       </c>
-      <c r="C209" t="s">
-        <v>0</v>
-      </c>
-      <c r="D209">
+      <c r="C209">
         <v>1016</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>209</v>
       </c>
       <c r="B210">
         <v>1400</v>
       </c>
-      <c r="C210" t="s">
-        <v>0</v>
-      </c>
-      <c r="D210">
+      <c r="C210">
         <v>504</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>210</v>
       </c>
       <c r="B211">
         <v>1400</v>
       </c>
-      <c r="C211" t="s">
-        <v>0</v>
-      </c>
-      <c r="D211">
+      <c r="C211">
         <v>5592</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>211</v>
       </c>
       <c r="B212">
         <v>1384</v>
       </c>
-      <c r="C212" t="s">
-        <v>0</v>
-      </c>
-      <c r="D212">
+      <c r="C212">
         <v>-168</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>212</v>
       </c>
       <c r="B213">
         <v>1384</v>
       </c>
-      <c r="C213" t="s">
-        <v>0</v>
-      </c>
-      <c r="D213">
+      <c r="C213">
         <v>4280</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>213</v>
       </c>
       <c r="B214">
         <v>1368</v>
       </c>
-      <c r="C214" t="s">
-        <v>0</v>
-      </c>
-      <c r="D214">
+      <c r="C214">
         <v>-616</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>214</v>
       </c>
       <c r="B215">
         <v>1368</v>
       </c>
-      <c r="C215" t="s">
-        <v>0</v>
-      </c>
-      <c r="D215">
+      <c r="C215">
         <v>4584</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>215</v>
       </c>
       <c r="B216">
         <v>1352</v>
       </c>
-      <c r="C216" t="s">
-        <v>0</v>
-      </c>
-      <c r="D216">
+      <c r="C216">
         <v>-5064</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>216</v>
       </c>
       <c r="B217">
         <v>1352</v>
       </c>
-      <c r="C217" t="s">
-        <v>0</v>
-      </c>
-      <c r="D217">
+      <c r="C217">
         <v>-1896</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>217</v>
       </c>
       <c r="B218">
         <v>1352</v>
       </c>
-      <c r="C218" t="s">
-        <v>0</v>
-      </c>
-      <c r="D218">
+      <c r="C218">
         <v>-776</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>218</v>
       </c>
       <c r="B219">
         <v>1352</v>
       </c>
-      <c r="C219" t="s">
-        <v>0</v>
-      </c>
-      <c r="D219">
+      <c r="C219">
         <v>760</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>219</v>
       </c>
       <c r="B220">
         <v>1352</v>
       </c>
-      <c r="C220" t="s">
-        <v>0</v>
-      </c>
-      <c r="D220">
+      <c r="C220">
         <v>3912</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>220</v>
       </c>
       <c r="B221">
         <v>1352</v>
       </c>
-      <c r="C221" t="s">
-        <v>0</v>
-      </c>
-      <c r="D221">
+      <c r="C221">
         <v>4936</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>221</v>
       </c>
       <c r="B222">
         <v>1336</v>
       </c>
-      <c r="C222" t="s">
-        <v>0</v>
-      </c>
-      <c r="D222">
+      <c r="C222">
         <v>-1448</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>222</v>
       </c>
       <c r="B223">
         <v>1336</v>
       </c>
-      <c r="C223" t="s">
-        <v>0</v>
-      </c>
-      <c r="D223">
+      <c r="C223">
         <v>-1096</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>223</v>
       </c>
       <c r="B224">
         <v>1320</v>
       </c>
-      <c r="C224" t="s">
-        <v>0</v>
-      </c>
-      <c r="D224">
+      <c r="C224">
         <v>56</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>224</v>
       </c>
       <c r="B225">
         <v>1304</v>
       </c>
-      <c r="C225" t="s">
-        <v>0</v>
-      </c>
-      <c r="D225">
+      <c r="C225">
         <v>-2792</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>225</v>
       </c>
       <c r="B226">
         <v>1304</v>
       </c>
-      <c r="C226" t="s">
-        <v>0</v>
-      </c>
-      <c r="D226">
+      <c r="C226">
         <v>1976</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>226</v>
       </c>
       <c r="B227">
         <v>1144</v>
       </c>
-      <c r="C227" t="s">
-        <v>0</v>
-      </c>
-      <c r="D227">
+      <c r="C227">
         <v>3032</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>227</v>
       </c>
       <c r="B228">
         <v>1128</v>
       </c>
-      <c r="C228" t="s">
-        <v>0</v>
-      </c>
-      <c r="D228">
+      <c r="C228">
         <v>-1528</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>228</v>
       </c>
       <c r="B229">
         <v>1128</v>
       </c>
-      <c r="C229" t="s">
-        <v>0</v>
-      </c>
-      <c r="D229">
+      <c r="C229">
         <v>-904</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>229</v>
       </c>
       <c r="B230">
         <v>1128</v>
       </c>
-      <c r="C230" t="s">
-        <v>0</v>
-      </c>
-      <c r="D230">
+      <c r="C230">
         <v>3960</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>230</v>
       </c>
       <c r="B231">
         <v>1128</v>
       </c>
-      <c r="C231" t="s">
-        <v>0</v>
-      </c>
-      <c r="D231">
+      <c r="C231">
         <v>4568</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>231</v>
       </c>
       <c r="B232">
         <v>1112</v>
       </c>
-      <c r="C232" t="s">
-        <v>0</v>
-      </c>
-      <c r="D232">
+      <c r="C232">
         <v>-3016</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>232</v>
       </c>
       <c r="B233">
         <v>1112</v>
       </c>
-      <c r="C233" t="s">
-        <v>0</v>
-      </c>
-      <c r="D233">
+      <c r="C233">
         <v>328</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>233</v>
       </c>
       <c r="B234">
         <v>1096</v>
       </c>
-      <c r="C234" t="s">
-        <v>0</v>
-      </c>
-      <c r="D234">
+      <c r="C234">
         <v>-2536</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>234</v>
       </c>
       <c r="B235">
         <v>1096</v>
       </c>
-      <c r="C235" t="s">
-        <v>0</v>
-      </c>
-      <c r="D235">
+      <c r="C235">
         <v>-1896</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>235</v>
       </c>
       <c r="B236">
         <v>1080</v>
       </c>
-      <c r="C236" t="s">
-        <v>0</v>
-      </c>
-      <c r="D236">
+      <c r="C236">
         <v>-3448</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>236</v>
       </c>
       <c r="B237">
         <v>1080</v>
       </c>
-      <c r="C237" t="s">
-        <v>0</v>
-      </c>
-      <c r="D237">
+      <c r="C237">
         <v>4840</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>237</v>
       </c>
       <c r="B238">
         <v>1064</v>
       </c>
-      <c r="C238" t="s">
-        <v>0</v>
-      </c>
-      <c r="D238">
+      <c r="C238">
         <v>664</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>238</v>
       </c>
       <c r="B239">
         <v>1048</v>
       </c>
-      <c r="C239" t="s">
-        <v>0</v>
-      </c>
-      <c r="D239">
+      <c r="C239">
         <v>-5080</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>239</v>
       </c>
       <c r="B240">
         <v>1048</v>
       </c>
-      <c r="C240" t="s">
-        <v>0</v>
-      </c>
-      <c r="D240">
+      <c r="C240">
         <v>1064</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>240</v>
       </c>
       <c r="B241">
         <v>1048</v>
       </c>
-      <c r="C241" t="s">
-        <v>0</v>
-      </c>
-      <c r="D241">
+      <c r="C241">
         <v>1288</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>241</v>
       </c>
       <c r="B242">
         <v>1032</v>
       </c>
-      <c r="C242" t="s">
-        <v>0</v>
-      </c>
-      <c r="D242">
+      <c r="C242">
         <v>-1192</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>242</v>
       </c>
       <c r="B243">
         <v>1032</v>
       </c>
-      <c r="C243" t="s">
-        <v>0</v>
-      </c>
-      <c r="D243">
+      <c r="C243">
         <v>-600</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>243</v>
       </c>
       <c r="B244">
         <v>1032</v>
       </c>
-      <c r="C244" t="s">
-        <v>0</v>
-      </c>
-      <c r="D244">
+      <c r="C244">
         <v>2296</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>244</v>
       </c>
       <c r="B245">
         <v>1016</v>
       </c>
-      <c r="C245" t="s">
-        <v>0</v>
-      </c>
-      <c r="D245">
+      <c r="C245">
         <v>5560</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>245</v>
       </c>
       <c r="B246">
         <v>1000</v>
       </c>
-      <c r="C246" t="s">
-        <v>0</v>
-      </c>
-      <c r="D246">
+      <c r="C246">
         <v>5896</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>246</v>
       </c>
       <c r="B247">
         <v>968</v>
       </c>
-      <c r="C247" t="s">
-        <v>0</v>
-      </c>
-      <c r="D247">
+      <c r="C247">
         <v>-2088</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>247</v>
       </c>
       <c r="B248">
         <v>968</v>
       </c>
-      <c r="C248" t="s">
-        <v>0</v>
-      </c>
-      <c r="D248">
+      <c r="C248">
         <v>5176</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>248</v>
       </c>
       <c r="B249">
         <v>808</v>
       </c>
-      <c r="C249" t="s">
-        <v>0</v>
-      </c>
-      <c r="D249">
+      <c r="C249">
         <v>-904</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>249</v>
       </c>
       <c r="B250">
         <v>792</v>
       </c>
-      <c r="C250" t="s">
-        <v>0</v>
-      </c>
-      <c r="D250">
+      <c r="C250">
         <v>424</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>250</v>
       </c>
       <c r="B251">
         <v>792</v>
       </c>
-      <c r="C251" t="s">
-        <v>0</v>
-      </c>
-      <c r="D251">
+      <c r="C251">
         <v>984</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>251</v>
       </c>
       <c r="B252">
         <v>792</v>
       </c>
-      <c r="C252" t="s">
-        <v>0</v>
-      </c>
-      <c r="D252">
+      <c r="C252">
         <v>1352</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>252</v>
       </c>
       <c r="B253">
         <v>792</v>
       </c>
-      <c r="C253" t="s">
-        <v>0</v>
-      </c>
-      <c r="D253">
+      <c r="C253">
         <v>5192</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>253</v>
       </c>
       <c r="B254">
         <v>776</v>
       </c>
-      <c r="C254" t="s">
-        <v>0</v>
-      </c>
-      <c r="D254">
+      <c r="C254">
         <v>-2392</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>254</v>
       </c>
       <c r="B255">
         <v>776</v>
       </c>
-      <c r="C255" t="s">
-        <v>0</v>
-      </c>
-      <c r="D255">
+      <c r="C255">
         <v>-296</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>255</v>
       </c>
       <c r="B256">
         <v>776</v>
       </c>
-      <c r="C256" t="s">
-        <v>0</v>
-      </c>
-      <c r="D256">
+      <c r="C256">
         <v>4216</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>256</v>
       </c>
       <c r="B257">
         <v>776</v>
       </c>
-      <c r="C257" t="s">
-        <v>0</v>
-      </c>
-      <c r="D257">
+      <c r="C257">
         <v>5512</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>257</v>
       </c>
       <c r="B258">
         <v>760</v>
       </c>
-      <c r="C258" t="s">
-        <v>0</v>
-      </c>
-      <c r="D258">
+      <c r="C258">
         <v>-3768</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>258</v>
       </c>
       <c r="B259">
         <v>760</v>
       </c>
-      <c r="C259" t="s">
-        <v>0</v>
-      </c>
-      <c r="D259">
+      <c r="C259">
         <v>-568</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>259</v>
       </c>
       <c r="B260">
         <v>744</v>
       </c>
-      <c r="C260" t="s">
-        <v>0</v>
-      </c>
-      <c r="D260">
+      <c r="C260">
         <v>-2712</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>260</v>
       </c>
       <c r="B261">
         <v>744</v>
       </c>
-      <c r="C261" t="s">
-        <v>0</v>
-      </c>
-      <c r="D261">
+      <c r="C261">
         <v>4600</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>261</v>
       </c>
       <c r="B262">
         <v>728</v>
       </c>
-      <c r="C262" t="s">
-        <v>0</v>
-      </c>
-      <c r="D262">
+      <c r="C262">
         <v>-4984</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>262</v>
       </c>
       <c r="B263">
         <v>728</v>
       </c>
-      <c r="C263" t="s">
-        <v>0</v>
-      </c>
-      <c r="D263">
+      <c r="C263">
         <v>-4440</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>263</v>
       </c>
       <c r="B264">
         <v>728</v>
       </c>
-      <c r="C264" t="s">
-        <v>0</v>
-      </c>
-      <c r="D264">
+      <c r="C264">
         <v>-3464</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>264</v>
       </c>
       <c r="B265">
         <v>728</v>
       </c>
-      <c r="C265" t="s">
-        <v>0</v>
-      </c>
-      <c r="D265">
+      <c r="C265">
         <v>2984</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>265</v>
       </c>
       <c r="B266">
         <v>728</v>
       </c>
-      <c r="C266" t="s">
-        <v>0</v>
-      </c>
-      <c r="D266">
+      <c r="C266">
         <v>5880</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>266</v>
       </c>
       <c r="B267">
         <v>712</v>
       </c>
-      <c r="C267" t="s">
-        <v>0</v>
-      </c>
-      <c r="D267">
+      <c r="C267">
         <v>-2184</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>267</v>
       </c>
       <c r="B268">
         <v>696</v>
       </c>
-      <c r="C268" t="s">
-        <v>0</v>
-      </c>
-      <c r="D268">
+      <c r="C268">
         <v>-6024</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>268</v>
       </c>
       <c r="B269">
         <v>696</v>
       </c>
-      <c r="C269" t="s">
-        <v>0</v>
-      </c>
-      <c r="D269">
+      <c r="C269">
         <v>-1864</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>269</v>
       </c>
       <c r="B270">
         <v>696</v>
       </c>
-      <c r="C270" t="s">
-        <v>0</v>
-      </c>
-      <c r="D270">
+      <c r="C270">
         <v>-1128</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>270</v>
       </c>
       <c r="B271">
         <v>680</v>
       </c>
-      <c r="C271" t="s">
-        <v>0</v>
-      </c>
-      <c r="D271">
+      <c r="C271">
         <v>-3016</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>271</v>
       </c>
       <c r="B272">
         <v>648</v>
       </c>
-      <c r="C272" t="s">
-        <v>0</v>
-      </c>
-      <c r="D272">
+      <c r="C272">
         <v>-5608</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>272</v>
       </c>
       <c r="B273">
         <v>648</v>
       </c>
-      <c r="C273" t="s">
-        <v>0</v>
-      </c>
-      <c r="D273">
+      <c r="C273">
         <v>-4632</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>273</v>
       </c>
       <c r="B274">
         <v>472</v>
       </c>
-      <c r="C274" t="s">
-        <v>0</v>
-      </c>
-      <c r="D274">
+      <c r="C274">
         <v>-1896</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>274</v>
       </c>
       <c r="B275">
         <v>472</v>
       </c>
-      <c r="C275" t="s">
-        <v>0</v>
-      </c>
-      <c r="D275">
+      <c r="C275">
         <v>-1480</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>275</v>
       </c>
       <c r="B276">
         <v>472</v>
       </c>
-      <c r="C276" t="s">
-        <v>0</v>
-      </c>
-      <c r="D276">
+      <c r="C276">
         <v>4664</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>276</v>
       </c>
       <c r="B277">
         <v>456</v>
       </c>
-      <c r="C277" t="s">
-        <v>0</v>
-      </c>
-      <c r="D277">
+      <c r="C277">
         <v>-4712</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>277</v>
       </c>
       <c r="B278">
         <v>456</v>
       </c>
-      <c r="C278" t="s">
-        <v>0</v>
-      </c>
-      <c r="D278">
+      <c r="C278">
         <v>-3976</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>278</v>
       </c>
       <c r="B279">
         <v>456</v>
       </c>
-      <c r="C279" t="s">
-        <v>0</v>
-      </c>
-      <c r="D279">
+      <c r="C279">
         <v>-2760</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>279</v>
       </c>
       <c r="B280">
         <v>456</v>
       </c>
-      <c r="C280" t="s">
-        <v>0</v>
-      </c>
-      <c r="D280">
+      <c r="C280">
         <v>-872</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>280</v>
       </c>
       <c r="B281">
         <v>440</v>
       </c>
-      <c r="C281" t="s">
-        <v>0</v>
-      </c>
-      <c r="D281">
+      <c r="C281">
         <v>-1256</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>281</v>
       </c>
       <c r="B282">
         <v>440</v>
       </c>
-      <c r="C282" t="s">
-        <v>0</v>
-      </c>
-      <c r="D282">
+      <c r="C282">
         <v>1288</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>282</v>
       </c>
       <c r="B283">
         <v>440</v>
       </c>
-      <c r="C283" t="s">
-        <v>0</v>
-      </c>
-      <c r="D283">
+      <c r="C283">
         <v>5304</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>283</v>
       </c>
       <c r="B284">
         <v>440</v>
       </c>
-      <c r="C284" t="s">
-        <v>0</v>
-      </c>
-      <c r="D284">
+      <c r="C284">
         <v>5944</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>284</v>
       </c>
       <c r="B285">
         <v>408</v>
       </c>
-      <c r="C285" t="s">
-        <v>0</v>
-      </c>
-      <c r="D285">
+      <c r="C285">
         <v>-4456</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>285</v>
       </c>
       <c r="B286">
         <v>408</v>
       </c>
-      <c r="C286" t="s">
-        <v>0</v>
-      </c>
-      <c r="D286">
+      <c r="C286">
         <v>-3176</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>286</v>
       </c>
       <c r="B287">
         <v>408</v>
       </c>
-      <c r="C287" t="s">
-        <v>0</v>
-      </c>
-      <c r="D287">
+      <c r="C287">
         <v>-600</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>287</v>
       </c>
       <c r="B288">
         <v>408</v>
       </c>
-      <c r="C288" t="s">
-        <v>0</v>
-      </c>
-      <c r="D288">
+      <c r="C288">
         <v>5496</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>288</v>
       </c>
       <c r="B289">
         <v>392</v>
       </c>
-      <c r="C289" t="s">
-        <v>0</v>
-      </c>
-      <c r="D289">
+      <c r="C289">
         <v>-3512</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>289</v>
       </c>
       <c r="B290">
         <v>392</v>
       </c>
-      <c r="C290" t="s">
-        <v>0</v>
-      </c>
-      <c r="D290">
+      <c r="C290">
         <v>328</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>290</v>
       </c>
       <c r="B291">
         <v>360</v>
       </c>
-      <c r="C291" t="s">
-        <v>0</v>
-      </c>
-      <c r="D291">
+      <c r="C291">
         <v>-2552</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>291</v>
       </c>
       <c r="B292">
         <v>360</v>
       </c>
-      <c r="C292" t="s">
-        <v>0</v>
-      </c>
-      <c r="D292">
+      <c r="C292">
         <v>728</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>292</v>
       </c>
       <c r="B293">
         <v>360</v>
       </c>
-      <c r="C293" t="s">
-        <v>0</v>
-      </c>
-      <c r="D293">
+      <c r="C293">
         <v>1032</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>293</v>
       </c>
       <c r="B294">
         <v>344</v>
       </c>
-      <c r="C294" t="s">
-        <v>0</v>
-      </c>
-      <c r="D294">
+      <c r="C294">
         <v>-136</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>294</v>
       </c>
       <c r="B295">
         <v>344</v>
       </c>
-      <c r="C295" t="s">
-        <v>0</v>
-      </c>
-      <c r="D295">
+      <c r="C295">
         <v>168</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>295</v>
       </c>
       <c r="B296">
         <v>328</v>
       </c>
-      <c r="C296" t="s">
-        <v>0</v>
-      </c>
-      <c r="D296">
+      <c r="C296">
         <v>-5928</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>296</v>
       </c>
       <c r="B297">
         <v>184</v>
       </c>
-      <c r="C297" t="s">
-        <v>0</v>
-      </c>
-      <c r="D297">
+      <c r="C297">
         <v>-5080</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>297</v>
       </c>
       <c r="B298">
         <v>168</v>
       </c>
-      <c r="C298" t="s">
-        <v>0</v>
-      </c>
-      <c r="D298">
+      <c r="C298">
         <v>-3352</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>298</v>
       </c>
       <c r="B299">
         <v>168</v>
       </c>
-      <c r="C299" t="s">
-        <v>0</v>
-      </c>
-      <c r="D299">
+      <c r="C299">
         <v>-776</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>299</v>
       </c>
       <c r="B300">
         <v>152</v>
       </c>
-      <c r="C300" t="s">
-        <v>0</v>
-      </c>
-      <c r="D300">
+      <c r="C300">
         <v>-1416</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>300</v>
       </c>
       <c r="B301">
         <v>152</v>
       </c>
-      <c r="C301" t="s">
-        <v>0</v>
-      </c>
-      <c r="D301">
+      <c r="C301">
         <v>1064</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>301</v>
       </c>
       <c r="B302">
         <v>136</v>
       </c>
-      <c r="C302" t="s">
-        <v>0</v>
-      </c>
-      <c r="D302">
+      <c r="C302">
         <v>-4136</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>302</v>
       </c>
       <c r="B303">
         <v>104</v>
       </c>
-      <c r="C303" t="s">
-        <v>0</v>
-      </c>
-      <c r="D303">
+      <c r="C303">
         <v>-2392</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>303</v>
       </c>
       <c r="B304">
         <v>88</v>
       </c>
-      <c r="C304" t="s">
-        <v>0</v>
-      </c>
-      <c r="D304">
+      <c r="C304">
         <v>-1752</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>304</v>
       </c>
       <c r="B305">
         <v>88</v>
       </c>
-      <c r="C305" t="s">
-        <v>0</v>
-      </c>
-      <c r="D305">
+      <c r="C305">
         <v>1400</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>305</v>
       </c>
       <c r="B306">
         <v>72</v>
       </c>
-      <c r="C306" t="s">
-        <v>0</v>
-      </c>
-      <c r="D306">
+      <c r="C306">
         <v>-216</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>306</v>
       </c>
       <c r="B307">
         <v>72</v>
       </c>
-      <c r="C307" t="s">
-        <v>0</v>
-      </c>
-      <c r="D307">
+      <c r="C307">
         <v>776</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>307</v>
       </c>
       <c r="B308">
         <v>56</v>
       </c>
-      <c r="C308" t="s">
-        <v>0</v>
-      </c>
-      <c r="D308">
+      <c r="C308">
         <v>-3176</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>308</v>
       </c>
       <c r="B309">
         <v>56</v>
       </c>
-      <c r="C309" t="s">
-        <v>0</v>
-      </c>
-      <c r="D309">
+      <c r="C309">
         <v>360</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>309</v>
       </c>
       <c r="B310">
         <v>40</v>
       </c>
-      <c r="C310" t="s">
-        <v>0</v>
-      </c>
-      <c r="D310">
+      <c r="C310">
         <v>-5752</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>310</v>
       </c>
       <c r="B311">
         <v>40</v>
       </c>
-      <c r="C311" t="s">
-        <v>0</v>
-      </c>
-      <c r="D311">
+      <c r="C311">
         <v>-2104</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>311</v>
       </c>
       <c r="B312">
         <v>40</v>
       </c>
-      <c r="C312" t="s">
-        <v>0</v>
-      </c>
-      <c r="D312">
+      <c r="C312">
         <v>120</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>312</v>
       </c>
       <c r="B313">
         <v>8</v>
       </c>
-      <c r="C313" t="s">
-        <v>0</v>
-      </c>
-      <c r="D313">
+      <c r="C313">
         <v>-2760</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>313</v>
       </c>
       <c r="B314">
         <v>-136</v>
       </c>
-      <c r="C314" t="s">
-        <v>0</v>
-      </c>
-      <c r="D314">
+      <c r="C314">
         <v>-5720</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>314</v>
       </c>
       <c r="B315">
         <v>-152</v>
       </c>
-      <c r="C315" t="s">
-        <v>0</v>
-      </c>
-      <c r="D315">
+      <c r="C315">
         <v>-5320</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>315</v>
       </c>
       <c r="B316">
         <v>-152</v>
       </c>
-      <c r="C316" t="s">
-        <v>0</v>
-      </c>
-      <c r="D316">
+      <c r="C316">
         <v>792</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>316</v>
       </c>
       <c r="B317">
         <v>-168</v>
       </c>
-      <c r="C317" t="s">
-        <v>0</v>
-      </c>
-      <c r="D317">
+      <c r="C317">
         <v>-1768</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>317</v>
       </c>
       <c r="B318">
         <v>-168</v>
       </c>
-      <c r="C318" t="s">
-        <v>0</v>
-      </c>
-      <c r="D318">
+      <c r="C318">
         <v>-3192</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>318</v>
       </c>
       <c r="B319">
         <v>-200</v>
       </c>
-      <c r="C319" t="s">
-        <v>0</v>
-      </c>
-      <c r="D319">
+      <c r="C319">
         <v>-2232</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>319</v>
       </c>
       <c r="B320">
         <v>-296</v>
       </c>
-      <c r="C320" t="s">
-        <v>0</v>
-      </c>
-      <c r="D320">
+      <c r="C320">
         <v>-2376</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>320</v>
       </c>
       <c r="B321">
         <v>-312</v>
       </c>
-      <c r="C321" t="s">
-        <v>0</v>
-      </c>
-      <c r="D321">
+      <c r="C321">
         <v>1112</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>321</v>
       </c>
       <c r="B322">
         <v>-456</v>
       </c>
-      <c r="C322" t="s">
-        <v>0</v>
-      </c>
-      <c r="D322">
+      <c r="C322">
         <v>792</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>322</v>
       </c>
       <c r="B323">
         <v>-488</v>
       </c>
-      <c r="C323" t="s">
-        <v>0</v>
-      </c>
-      <c r="D323">
+      <c r="C323">
         <v>1144</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>323</v>
       </c>
       <c r="B324">
         <v>-504</v>
       </c>
-      <c r="C324" t="s">
-        <v>0</v>
-      </c>
-      <c r="D324">
+      <c r="C324">
         <v>-3080</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>324</v>
       </c>
       <c r="B325">
         <v>-504</v>
       </c>
-      <c r="C325" t="s">
-        <v>0</v>
-      </c>
-      <c r="D325">
+      <c r="C325">
         <v>-2856</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>325</v>
       </c>
       <c r="B326">
         <v>-504</v>
       </c>
-      <c r="C326" t="s">
-        <v>0</v>
-      </c>
-      <c r="D326">
+      <c r="C326">
         <v>-1912</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A327">
         <v>326</v>
       </c>
       <c r="B327">
         <v>-504</v>
       </c>
-      <c r="C327" t="s">
-        <v>0</v>
-      </c>
-      <c r="D327">
+      <c r="C327">
         <v>-2088</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>327</v>
       </c>
       <c r="B328">
         <v>-536</v>
       </c>
-      <c r="C328" t="s">
-        <v>0</v>
-      </c>
-      <c r="D328">
+      <c r="C328">
         <v>-6056</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>328</v>
       </c>
       <c r="B329">
         <v>-536</v>
       </c>
-      <c r="C329" t="s">
-        <v>0</v>
-      </c>
-      <c r="D329">
+      <c r="C329">
         <v>-1592</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>329</v>
       </c>
       <c r="B330">
         <v>-568</v>
       </c>
-      <c r="C330" t="s">
-        <v>0</v>
-      </c>
-      <c r="D330">
+      <c r="C330">
         <v>2024</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>330</v>
       </c>
       <c r="B331">
         <v>-600</v>
       </c>
-      <c r="C331" t="s">
-        <v>0</v>
-      </c>
-      <c r="D331">
+      <c r="C331">
         <v>1704</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>331</v>
       </c>
       <c r="B332">
         <v>-600</v>
       </c>
-      <c r="C332" t="s">
-        <v>0</v>
-      </c>
-      <c r="D332">
+      <c r="C332">
         <v>2280</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>332</v>
       </c>
       <c r="B333">
         <v>-776</v>
       </c>
-      <c r="C333" t="s">
-        <v>0</v>
-      </c>
-      <c r="D333">
+      <c r="C333">
         <v>152</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>333</v>
       </c>
       <c r="B334">
         <v>-792</v>
       </c>
-      <c r="C334" t="s">
-        <v>0</v>
-      </c>
-      <c r="D334">
+      <c r="C334">
         <v>5480</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>334</v>
       </c>
       <c r="B335">
         <v>-824</v>
       </c>
-      <c r="C335" t="s">
-        <v>0</v>
-      </c>
-      <c r="D335">
+      <c r="C335">
         <v>1656</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>335</v>
       </c>
       <c r="B336">
         <v>-840</v>
       </c>
-      <c r="C336" t="s">
-        <v>0</v>
-      </c>
-      <c r="D336">
+      <c r="C336">
         <v>-5032</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>336</v>
       </c>
       <c r="B337">
         <v>-840</v>
       </c>
-      <c r="C337" t="s">
-        <v>0</v>
-      </c>
-      <c r="D337">
+      <c r="C337">
         <v>4616</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>337</v>
       </c>
       <c r="B338">
         <v>-840</v>
       </c>
-      <c r="C338" t="s">
-        <v>0</v>
-      </c>
-      <c r="D338">
+      <c r="C338">
         <v>5192</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>338</v>
       </c>
       <c r="B339">
         <v>-904</v>
       </c>
-      <c r="C339" t="s">
-        <v>0</v>
-      </c>
-      <c r="D339">
+      <c r="C339">
         <v>4168</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>339</v>
       </c>
       <c r="B340">
         <v>-920</v>
       </c>
-      <c r="C340" t="s">
-        <v>0</v>
-      </c>
-      <c r="D340">
+      <c r="C340">
         <v>1384</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>340</v>
       </c>
       <c r="B341">
         <v>-936</v>
       </c>
-      <c r="C341" t="s">
-        <v>0</v>
-      </c>
-      <c r="D341">
+      <c r="C341">
         <v>792</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>341</v>
       </c>
       <c r="B342">
         <v>-952</v>
       </c>
-      <c r="C342" t="s">
-        <v>0</v>
-      </c>
-      <c r="D342">
+      <c r="C342">
         <v>5912</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>342</v>
       </c>
       <c r="B343">
         <v>-1128</v>
       </c>
-      <c r="C343" t="s">
-        <v>0</v>
-      </c>
-      <c r="D343">
+      <c r="C343">
         <v>1304</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>343</v>
       </c>
       <c r="B344">
         <v>-1128</v>
       </c>
-      <c r="C344" t="s">
-        <v>0</v>
-      </c>
-      <c r="D344">
+      <c r="C344">
         <v>4952</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>344</v>
       </c>
       <c r="B345">
         <v>-1160</v>
       </c>
-      <c r="C345" t="s">
-        <v>0</v>
-      </c>
-      <c r="D345">
+      <c r="C345">
         <v>-1416</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>345</v>
       </c>
       <c r="B346">
         <v>-1160</v>
       </c>
-      <c r="C346" t="s">
-        <v>0</v>
-      </c>
-      <c r="D346">
+      <c r="C346">
         <v>3672</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>346</v>
       </c>
       <c r="B347">
         <v>-1176</v>
       </c>
-      <c r="C347" t="s">
-        <v>0</v>
-      </c>
-      <c r="D347">
+      <c r="C347">
         <v>-4648</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A348">
         <v>347</v>
       </c>
       <c r="B348">
         <v>-1176</v>
       </c>
-      <c r="C348" t="s">
-        <v>0</v>
-      </c>
-      <c r="D348">
+      <c r="C348">
         <v>1048</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>348</v>
       </c>
       <c r="B349">
         <v>-1176</v>
       </c>
-      <c r="C349" t="s">
-        <v>0</v>
-      </c>
-      <c r="D349">
+      <c r="C349">
         <v>1992</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>349</v>
       </c>
       <c r="B350">
         <v>-1176</v>
       </c>
-      <c r="C350" t="s">
-        <v>0</v>
-      </c>
-      <c r="D350">
+      <c r="C350">
         <v>4616</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A351">
         <v>350</v>
       </c>
       <c r="B351">
         <v>-1192</v>
       </c>
-      <c r="C351" t="s">
-        <v>0</v>
-      </c>
-      <c r="D351">
+      <c r="C351">
         <v>5224</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A352">
         <v>351</v>
       </c>
       <c r="B352">
         <v>-1224</v>
       </c>
-      <c r="C352" t="s">
-        <v>0</v>
-      </c>
-      <c r="D352">
+      <c r="C352">
         <v>-4936</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A353">
         <v>352</v>
       </c>
       <c r="B353">
         <v>-1224</v>
       </c>
-      <c r="C353" t="s">
-        <v>0</v>
-      </c>
-      <c r="D353">
+      <c r="C353">
         <v>776</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>353</v>
       </c>
       <c r="B354">
         <v>-1240</v>
       </c>
-      <c r="C354" t="s">
-        <v>0</v>
-      </c>
-      <c r="D354">
+      <c r="C354">
         <v>3928</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>354</v>
       </c>
       <c r="B355">
         <v>-1240</v>
       </c>
-      <c r="C355" t="s">
-        <v>0</v>
-      </c>
-      <c r="D355">
+      <c r="C355">
         <v>5448</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>355</v>
       </c>
       <c r="B356">
         <v>-1256</v>
       </c>
-      <c r="C356" t="s">
-        <v>0</v>
-      </c>
-      <c r="D356">
+      <c r="C356">
         <v>-4344</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>356</v>
       </c>
       <c r="B357">
         <v>-1256</v>
       </c>
-      <c r="C357" t="s">
-        <v>0</v>
-      </c>
-      <c r="D357">
+      <c r="C357">
         <v>4328</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>357</v>
       </c>
       <c r="B358">
         <v>-1272</v>
       </c>
-      <c r="C358" t="s">
-        <v>0</v>
-      </c>
-      <c r="D358">
+      <c r="C358">
         <v>5848</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>358</v>
       </c>
       <c r="B359">
         <v>-1432</v>
       </c>
-      <c r="C359" t="s">
-        <v>0</v>
-      </c>
-      <c r="D359">
+      <c r="C359">
         <v>4008</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>359</v>
       </c>
       <c r="B360">
         <v>-1432</v>
       </c>
-      <c r="C360" t="s">
-        <v>0</v>
-      </c>
-      <c r="D360">
+      <c r="C360">
         <v>3624</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>360</v>
       </c>
       <c r="B361">
         <v>-1464</v>
       </c>
-      <c r="C361" t="s">
-        <v>0</v>
-      </c>
-      <c r="D361">
+      <c r="C361">
         <v>-5048</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>361</v>
       </c>
       <c r="B362">
         <v>-1464</v>
       </c>
-      <c r="C362" t="s">
-        <v>0</v>
-      </c>
-      <c r="D362">
+      <c r="C362">
         <v>5544</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>362</v>
       </c>
       <c r="B363">
         <v>-1496</v>
       </c>
-      <c r="C363" t="s">
-        <v>0</v>
-      </c>
-      <c r="D363">
+      <c r="C363">
         <v>-1480</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>363</v>
       </c>
       <c r="B364">
         <v>-1496</v>
       </c>
-      <c r="C364" t="s">
-        <v>0</v>
-      </c>
-      <c r="D364">
+      <c r="C364">
         <v>2584</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>364</v>
       </c>
       <c r="B365">
         <v>-1512</v>
       </c>
-      <c r="C365" t="s">
-        <v>0</v>
-      </c>
-      <c r="D365">
+      <c r="C365">
         <v>-1752</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>365</v>
       </c>
       <c r="B366">
         <v>-1528</v>
       </c>
-      <c r="C366" t="s">
-        <v>0</v>
-      </c>
-      <c r="D366">
+      <c r="C366">
         <v>-2104</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>366</v>
       </c>
       <c r="B367">
         <v>-1528</v>
       </c>
-      <c r="C367" t="s">
-        <v>0</v>
-      </c>
-      <c r="D367">
+      <c r="C367">
         <v>1400</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>367</v>
       </c>
       <c r="B368">
         <v>-1528</v>
       </c>
-      <c r="C368" t="s">
-        <v>0</v>
-      </c>
-      <c r="D368">
+      <c r="C368">
         <v>4200</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>368</v>
       </c>
       <c r="B369">
         <v>-1544</v>
       </c>
-      <c r="C369" t="s">
-        <v>0</v>
-      </c>
-      <c r="D369">
+      <c r="C369">
         <v>-4648</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>369</v>
       </c>
       <c r="B370">
         <v>-1544</v>
       </c>
-      <c r="C370" t="s">
-        <v>0</v>
-      </c>
-      <c r="D370">
+      <c r="C370">
         <v>2408</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>370</v>
       </c>
       <c r="B371">
         <v>-1544</v>
       </c>
-      <c r="C371" t="s">
-        <v>0</v>
-      </c>
-      <c r="D371">
+      <c r="C371">
         <v>3384</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>371</v>
       </c>
       <c r="B372">
         <v>-1560</v>
       </c>
-      <c r="C372" t="s">
-        <v>0</v>
-      </c>
-      <c r="D372">
+      <c r="C372">
         <v>4632</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>372</v>
       </c>
       <c r="B373">
         <v>-1576</v>
       </c>
-      <c r="C373" t="s">
-        <v>0</v>
-      </c>
-      <c r="D373">
+      <c r="C373">
         <v>5128</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>373</v>
       </c>
       <c r="B374">
         <v>-1592</v>
       </c>
-      <c r="C374" t="s">
-        <v>0</v>
-      </c>
-      <c r="D374">
+      <c r="C374">
         <v>2040</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>374</v>
       </c>
       <c r="B375">
         <v>-1592</v>
       </c>
-      <c r="C375" t="s">
-        <v>0</v>
-      </c>
-      <c r="D375">
+      <c r="C375">
         <v>3032</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>375</v>
       </c>
       <c r="B376">
         <v>-1592</v>
       </c>
-      <c r="C376" t="s">
-        <v>0</v>
-      </c>
-      <c r="D376">
+      <c r="C376">
         <v>4872</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>376</v>
       </c>
       <c r="B377">
         <v>-1752</v>
       </c>
-      <c r="C377" t="s">
-        <v>0</v>
-      </c>
-      <c r="D377">
+      <c r="C377">
         <v>-1416</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>377</v>
       </c>
       <c r="B378">
         <v>-1752</v>
       </c>
-      <c r="C378" t="s">
-        <v>0</v>
-      </c>
-      <c r="D378">
+      <c r="C378">
         <v>2376</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A379">
         <v>378</v>
       </c>
       <c r="B379">
         <v>-1752</v>
       </c>
-      <c r="C379" t="s">
-        <v>0</v>
-      </c>
-      <c r="D379">
+      <c r="C379">
         <v>5896</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A380">
         <v>379</v>
       </c>
       <c r="B380">
         <v>-1768</v>
       </c>
-      <c r="C380" t="s">
-        <v>0</v>
-      </c>
-      <c r="D380">
+      <c r="C380">
         <v>4200</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A381">
         <v>380</v>
       </c>
       <c r="B381">
         <v>-1784</v>
       </c>
-      <c r="C381" t="s">
-        <v>0</v>
-      </c>
-      <c r="D381">
+      <c r="C381">
         <v>1640</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>381</v>
       </c>
       <c r="B382">
         <v>-1800</v>
       </c>
-      <c r="C382" t="s">
-        <v>0</v>
-      </c>
-      <c r="D382">
+      <c r="C382">
         <v>3336</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>382</v>
       </c>
       <c r="B383">
         <v>-1800</v>
       </c>
-      <c r="C383" t="s">
-        <v>0</v>
-      </c>
-      <c r="D383">
+      <c r="C383">
         <v>4968</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>383</v>
       </c>
       <c r="B384">
         <v>-1816</v>
       </c>
-      <c r="C384" t="s">
-        <v>0</v>
-      </c>
-      <c r="D384">
+      <c r="C384">
         <v>-5640</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>384</v>
       </c>
       <c r="B385">
         <v>-1832</v>
       </c>
-      <c r="C385" t="s">
-        <v>0</v>
-      </c>
-      <c r="D385">
+      <c r="C385">
         <v>-1272</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A386">
         <v>385</v>
       </c>
       <c r="B386">
         <v>-1832</v>
       </c>
-      <c r="C386" t="s">
-        <v>0</v>
-      </c>
-      <c r="D386">
+      <c r="C386">
         <v>2056</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387">
         <v>386</v>
       </c>
       <c r="B387">
         <v>-1832</v>
       </c>
-      <c r="C387" t="s">
-        <v>0</v>
-      </c>
-      <c r="D387">
+      <c r="C387">
         <v>3576</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A388">
         <v>387</v>
       </c>
       <c r="B388">
         <v>-1848</v>
       </c>
-      <c r="C388" t="s">
-        <v>0</v>
-      </c>
-      <c r="D388">
+      <c r="C388">
         <v>-2136</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A389">
         <v>388</v>
       </c>
       <c r="B389">
         <v>-1864</v>
       </c>
-      <c r="C389" t="s">
-        <v>0</v>
-      </c>
-      <c r="D389">
+      <c r="C389">
         <v>-888</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A390">
         <v>389</v>
       </c>
       <c r="B390">
         <v>-1880</v>
       </c>
-      <c r="C390" t="s">
-        <v>0</v>
-      </c>
-      <c r="D390">
+      <c r="C390">
         <v>-4952</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A391">
         <v>390</v>
       </c>
       <c r="B391">
         <v>-1880</v>
       </c>
-      <c r="C391" t="s">
-        <v>0</v>
-      </c>
-      <c r="D391">
+      <c r="C391">
         <v>1448</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A392">
         <v>391</v>
       </c>
       <c r="B392">
         <v>-1880</v>
       </c>
-      <c r="C392" t="s">
-        <v>0</v>
-      </c>
-      <c r="D392">
+      <c r="C392">
         <v>5224</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A393">
         <v>392</v>
       </c>
       <c r="B393">
         <v>-1896</v>
       </c>
-      <c r="C393" t="s">
-        <v>0</v>
-      </c>
-      <c r="D393">
+      <c r="C393">
         <v>3880</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A394">
         <v>393</v>
       </c>
       <c r="B394">
         <v>-1896</v>
       </c>
-      <c r="C394" t="s">
-        <v>0</v>
-      </c>
-      <c r="D394">
+      <c r="C394">
         <v>3032</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A395">
         <v>394</v>
       </c>
       <c r="B395">
         <v>-1896</v>
       </c>
-      <c r="C395" t="s">
-        <v>0</v>
-      </c>
-      <c r="D395">
+      <c r="C395">
         <v>5448</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A396">
         <v>395</v>
       </c>
       <c r="B396">
         <v>-1912</v>
       </c>
-      <c r="C396" t="s">
-        <v>0</v>
-      </c>
-      <c r="D396">
+      <c r="C396">
         <v>-5272</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A397">
         <v>396</v>
       </c>
       <c r="B397">
         <v>-1912</v>
       </c>
-      <c r="C397" t="s">
-        <v>0</v>
-      </c>
-      <c r="D397">
+      <c r="C397">
         <v>1144</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398">
         <v>397</v>
       </c>
       <c r="B398">
         <v>-1912</v>
       </c>
-      <c r="C398" t="s">
-        <v>0</v>
-      </c>
-      <c r="D398">
+      <c r="C398">
         <v>4616</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A399">
         <v>398</v>
       </c>
       <c r="B399">
         <v>-2056</v>
       </c>
-      <c r="C399" t="s">
-        <v>0</v>
-      </c>
-      <c r="D399">
+      <c r="C399">
         <v>1768</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A400">
         <v>399</v>
       </c>
       <c r="B400">
         <v>-2056</v>
       </c>
-      <c r="C400" t="s">
-        <v>0</v>
-      </c>
-      <c r="D400">
+      <c r="C400">
         <v>3704</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A401">
         <v>400</v>
       </c>
       <c r="B401">
         <v>-2072</v>
       </c>
-      <c r="C401" t="s">
-        <v>0</v>
-      </c>
-      <c r="D401">
+      <c r="C401">
         <v>2056</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A402">
         <v>401</v>
       </c>
       <c r="B402">
         <v>-2088</v>
       </c>
-      <c r="C402" t="s">
-        <v>0</v>
-      </c>
-      <c r="D402">
+      <c r="C402">
         <v>4216</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A403">
         <v>402</v>
       </c>
       <c r="B403">
         <v>-2104</v>
       </c>
-      <c r="C403" t="s">
-        <v>0</v>
-      </c>
-      <c r="D403">
+      <c r="C403">
         <v>-5592</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A404">
         <v>403</v>
       </c>
       <c r="B404">
         <v>-2104</v>
       </c>
-      <c r="C404" t="s">
-        <v>0</v>
-      </c>
-      <c r="D404">
+      <c r="C404">
         <v>-5096</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A405">
         <v>404</v>
       </c>
       <c r="B405">
         <v>-2104</v>
       </c>
-      <c r="C405" t="s">
-        <v>0</v>
-      </c>
-      <c r="D405">
+      <c r="C405">
         <v>-3080</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A406">
         <v>405</v>
       </c>
       <c r="B406">
         <v>-2104</v>
       </c>
-      <c r="C406" t="s">
-        <v>0</v>
-      </c>
-      <c r="D406">
+      <c r="C406">
         <v>1352</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A407">
         <v>406</v>
       </c>
       <c r="B407">
         <v>-2120</v>
       </c>
-      <c r="C407" t="s">
-        <v>0</v>
-      </c>
-      <c r="D407">
+      <c r="C407">
         <v>-3368</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A408">
         <v>407</v>
       </c>
       <c r="B408">
         <v>-2136</v>
       </c>
-      <c r="C408" t="s">
-        <v>0</v>
-      </c>
-      <c r="D408">
+      <c r="C408">
         <v>-1160</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409">
         <v>408</v>
       </c>
       <c r="B409">
         <v>-2136</v>
       </c>
-      <c r="C409" t="s">
-        <v>0</v>
-      </c>
-      <c r="D409">
+      <c r="C409">
         <v>2632</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A410">
         <v>409</v>
       </c>
       <c r="B410">
         <v>-2152</v>
       </c>
-      <c r="C410" t="s">
-        <v>0</v>
-      </c>
-      <c r="D410">
+      <c r="C410">
         <v>2360</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A411">
         <v>410</v>
       </c>
       <c r="B411">
         <v>-2152</v>
       </c>
-      <c r="C411" t="s">
-        <v>0</v>
-      </c>
-      <c r="D411">
+      <c r="C411">
         <v>3896</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A412">
         <v>411</v>
       </c>
       <c r="B412">
         <v>-2152</v>
       </c>
-      <c r="C412" t="s">
-        <v>0</v>
-      </c>
-      <c r="D412">
+      <c r="C412">
         <v>3352</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A413">
         <v>412</v>
       </c>
       <c r="B413">
         <v>-2168</v>
       </c>
-      <c r="C413" t="s">
-        <v>0</v>
-      </c>
-      <c r="D413">
+      <c r="C413">
         <v>4824</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A414">
         <v>413</v>
       </c>
       <c r="B414">
         <v>-2184</v>
       </c>
-      <c r="C414" t="s">
-        <v>0</v>
-      </c>
-      <c r="D414">
+      <c r="C414">
         <v>-2872</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A415">
         <v>414</v>
       </c>
       <c r="B415">
         <v>-2184</v>
       </c>
-      <c r="C415" t="s">
-        <v>0</v>
-      </c>
-      <c r="D415">
+      <c r="C415">
         <v>4536</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A416">
         <v>415</v>
       </c>
       <c r="B416">
         <v>-2216</v>
       </c>
-      <c r="C416" t="s">
-        <v>0</v>
-      </c>
-      <c r="D416">
+      <c r="C416">
         <v>360</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A417">
         <v>416</v>
       </c>
       <c r="B417">
         <v>-2216</v>
       </c>
-      <c r="C417" t="s">
-        <v>0</v>
-      </c>
-      <c r="D417">
+      <c r="C417">
         <v>2984</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A418">
         <v>417</v>
       </c>
       <c r="B418">
         <v>-2232</v>
       </c>
-      <c r="C418" t="s">
-        <v>0</v>
-      </c>
-      <c r="D418">
+      <c r="C418">
         <v>-5416</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A419">
         <v>418</v>
       </c>
       <c r="B419">
         <v>-2376</v>
       </c>
-      <c r="C419" t="s">
-        <v>0</v>
-      </c>
-      <c r="D419">
+      <c r="C419">
         <v>4344</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420">
         <v>419</v>
       </c>
       <c r="B420">
         <v>-2376</v>
       </c>
-      <c r="C420" t="s">
-        <v>0</v>
-      </c>
-      <c r="D420">
+      <c r="C420">
         <v>4520</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A421">
         <v>420</v>
       </c>
       <c r="B421">
         <v>-2392</v>
       </c>
-      <c r="C421" t="s">
-        <v>0</v>
-      </c>
-      <c r="D421">
+      <c r="C421">
         <v>-5576</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A422">
         <v>421</v>
       </c>
       <c r="B422">
         <v>-2424</v>
       </c>
-      <c r="C422" t="s">
-        <v>0</v>
-      </c>
-      <c r="D422">
+      <c r="C422">
         <v>1944</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A423">
         <v>422</v>
       </c>
       <c r="B423">
         <v>-2440</v>
       </c>
-      <c r="C423" t="s">
-        <v>0</v>
-      </c>
-      <c r="D423">
+      <c r="C423">
         <v>-5368</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A424">
         <v>423</v>
       </c>
       <c r="B424">
         <v>-2440</v>
       </c>
-      <c r="C424" t="s">
-        <v>0</v>
-      </c>
-      <c r="D424">
+      <c r="C424">
         <v>-3480</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A425">
         <v>424</v>
       </c>
       <c r="B425">
         <v>-2440</v>
       </c>
-      <c r="C425" t="s">
-        <v>0</v>
-      </c>
-      <c r="D425">
+      <c r="C425">
         <v>-1432</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A426">
         <v>425</v>
       </c>
       <c r="B426">
         <v>-2440</v>
       </c>
-      <c r="C426" t="s">
-        <v>0</v>
-      </c>
-      <c r="D426">
+      <c r="C426">
         <v>4984</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A427">
         <v>426</v>
       </c>
       <c r="B427">
         <v>-2456</v>
       </c>
-      <c r="C427" t="s">
-        <v>0</v>
-      </c>
-      <c r="D427">
+      <c r="C427">
         <v>-3016</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A428">
         <v>427</v>
       </c>
       <c r="B428">
         <v>-2472</v>
       </c>
-      <c r="C428" t="s">
-        <v>0</v>
-      </c>
-      <c r="D428">
+      <c r="C428">
         <v>-5080</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A429">
         <v>428</v>
       </c>
       <c r="B429">
         <v>-2472</v>
       </c>
-      <c r="C429" t="s">
-        <v>0</v>
-      </c>
-      <c r="D429">
+      <c r="C429">
         <v>3256</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A430">
         <v>429</v>
       </c>
       <c r="B430">
         <v>-2488</v>
       </c>
-      <c r="C430" t="s">
-        <v>0</v>
-      </c>
-      <c r="D430">
+      <c r="C430">
         <v>2296</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431">
         <v>430</v>
       </c>
       <c r="B431">
         <v>-2488</v>
       </c>
-      <c r="C431" t="s">
-        <v>0</v>
-      </c>
-      <c r="D431">
+      <c r="C431">
         <v>3000</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A432">
         <v>431</v>
       </c>
       <c r="B432">
         <v>-2504</v>
       </c>
-      <c r="C432" t="s">
-        <v>0</v>
-      </c>
-      <c r="D432">
+      <c r="C432">
         <v>-5960</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A433">
         <v>432</v>
       </c>
       <c r="B433">
         <v>-2504</v>
       </c>
-      <c r="C433" t="s">
-        <v>0</v>
-      </c>
-      <c r="D433">
+      <c r="C433">
         <v>-1160</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A434">
         <v>433</v>
       </c>
       <c r="B434">
         <v>-2504</v>
       </c>
-      <c r="C434" t="s">
-        <v>0</v>
-      </c>
-      <c r="D434">
+      <c r="C434">
         <v>3528</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A435">
         <v>434</v>
       </c>
       <c r="B435">
         <v>-2504</v>
       </c>
-      <c r="C435" t="s">
-        <v>0</v>
-      </c>
-      <c r="D435">
+      <c r="C435">
         <v>2744</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A436">
         <v>435</v>
       </c>
       <c r="B436">
         <v>-2520</v>
       </c>
-      <c r="C436" t="s">
-        <v>0</v>
-      </c>
-      <c r="D436">
+      <c r="C436">
         <v>-3736</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A437">
         <v>436</v>
       </c>
       <c r="B437">
         <v>-2520</v>
       </c>
-      <c r="C437" t="s">
-        <v>0</v>
-      </c>
-      <c r="D437">
+      <c r="C437">
         <v>-232</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A438">
         <v>437</v>
       </c>
       <c r="B438">
         <v>-2536</v>
       </c>
-      <c r="C438" t="s">
-        <v>0</v>
-      </c>
-      <c r="D438">
+      <c r="C438">
         <v>-3992</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A439">
         <v>438</v>
       </c>
       <c r="B439">
         <v>-2552</v>
       </c>
-      <c r="C439" t="s">
-        <v>0</v>
-      </c>
-      <c r="D439">
+      <c r="C439">
         <v>-456</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A440">
         <v>439</v>
       </c>
       <c r="B440">
         <v>-2552</v>
       </c>
-      <c r="C440" t="s">
-        <v>0</v>
-      </c>
-      <c r="D440">
+      <c r="C440">
         <v>5240</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A441">
         <v>440</v>
       </c>
       <c r="B441">
         <v>-2696</v>
       </c>
-      <c r="C441" t="s">
-        <v>0</v>
-      </c>
-      <c r="D441">
+      <c r="C441">
         <v>-136</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442">
         <v>441</v>
       </c>
       <c r="B442">
         <v>-2696</v>
       </c>
-      <c r="C442" t="s">
-        <v>0</v>
-      </c>
-      <c r="D442">
+      <c r="C442">
         <v>4840</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A443">
         <v>442</v>
       </c>
       <c r="B443">
         <v>-2712</v>
       </c>
-      <c r="C443" t="s">
-        <v>0</v>
-      </c>
-      <c r="D443">
+      <c r="C443">
         <v>3576</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A444">
         <v>443</v>
       </c>
       <c r="B444">
         <v>-2760</v>
       </c>
-      <c r="C444" t="s">
-        <v>0</v>
-      </c>
-      <c r="D444">
+      <c r="C444">
         <v>88</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A445">
         <v>444</v>
       </c>
       <c r="B445">
         <v>-2792</v>
       </c>
-      <c r="C445" t="s">
-        <v>0</v>
-      </c>
-      <c r="D445">
+      <c r="C445">
         <v>-3816</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A446">
         <v>445</v>
       </c>
       <c r="B446">
         <v>-2808</v>
       </c>
-      <c r="C446" t="s">
-        <v>0</v>
-      </c>
-      <c r="D446">
+      <c r="C446">
         <v>-5352</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A447">
         <v>446</v>
       </c>
       <c r="B447">
         <v>-2808</v>
       </c>
-      <c r="C447" t="s">
-        <v>0</v>
-      </c>
-      <c r="D447">
+      <c r="C447">
         <v>-5080</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A448">
         <v>447</v>
       </c>
       <c r="B448">
         <v>-2808</v>
       </c>
-      <c r="C448" t="s">
-        <v>0</v>
-      </c>
-      <c r="D448">
+      <c r="C448">
         <v>3896</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A449">
         <v>448</v>
       </c>
       <c r="B449">
         <v>-2824</v>
       </c>
-      <c r="C449" t="s">
-        <v>0</v>
-      </c>
-      <c r="D449">
+      <c r="C449">
         <v>-5640</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A450">
         <v>449</v>
       </c>
       <c r="B450">
         <v>-2824</v>
       </c>
-      <c r="C450" t="s">
-        <v>0</v>
-      </c>
-      <c r="D450">
+      <c r="C450">
         <v>-2776</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A451">
         <v>450</v>
       </c>
       <c r="B451">
         <v>-2840</v>
       </c>
-      <c r="C451" t="s">
-        <v>0</v>
-      </c>
-      <c r="D451">
+      <c r="C451">
         <v>-616</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A452">
         <v>451</v>
       </c>
       <c r="B452">
         <v>-2840</v>
       </c>
-      <c r="C452" t="s">
-        <v>0</v>
-      </c>
-      <c r="D452">
+      <c r="C452">
         <v>2072</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453">
         <v>452</v>
       </c>
       <c r="B453">
         <v>-2840</v>
       </c>
-      <c r="C453" t="s">
-        <v>0</v>
-      </c>
-      <c r="D453">
+      <c r="C453">
         <v>2728</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A454">
         <v>453</v>
       </c>
       <c r="B454">
         <v>-2856</v>
       </c>
-      <c r="C454" t="s">
-        <v>0</v>
-      </c>
-      <c r="D454">
+      <c r="C454">
         <v>3384</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A455">
         <v>454</v>
       </c>
       <c r="B455">
         <v>-2872</v>
       </c>
-      <c r="C455" t="s">
-        <v>0</v>
-      </c>
-      <c r="D455">
+      <c r="C455">
         <v>-3128</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A456">
         <v>455</v>
       </c>
       <c r="B456">
         <v>-2872</v>
       </c>
-      <c r="C456" t="s">
-        <v>0</v>
-      </c>
-      <c r="D456">
+      <c r="C456">
         <v>-920</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A457">
         <v>456</v>
       </c>
       <c r="B457">
         <v>-3032</v>
       </c>
-      <c r="C457" t="s">
-        <v>0</v>
-      </c>
-      <c r="D457">
+      <c r="C457">
         <v>-584</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A458">
         <v>457</v>
       </c>
       <c r="B458">
         <v>-3048</v>
       </c>
-      <c r="C458" t="s">
-        <v>0</v>
-      </c>
-      <c r="D458">
+      <c r="C458">
         <v>3656</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A459">
         <v>458</v>
       </c>
       <c r="B459">
         <v>-3064</v>
       </c>
-      <c r="C459" t="s">
-        <v>0</v>
-      </c>
-      <c r="D459">
+      <c r="C459">
         <v>2648</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A460">
         <v>459</v>
       </c>
       <c r="B460">
         <v>-3096</v>
       </c>
-      <c r="C460" t="s">
-        <v>0</v>
-      </c>
-      <c r="D460">
+      <c r="C460">
         <v>-3096</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A461">
         <v>460</v>
       </c>
       <c r="B461">
         <v>-3096</v>
       </c>
-      <c r="C461" t="s">
-        <v>0</v>
-      </c>
-      <c r="D461">
+      <c r="C461">
         <v>40</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A462">
         <v>461</v>
       </c>
       <c r="B462">
         <v>-3112</v>
       </c>
-      <c r="C462" t="s">
-        <v>0</v>
-      </c>
-      <c r="D462">
+      <c r="C462">
         <v>-6024</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A463">
         <v>462</v>
       </c>
       <c r="B463">
         <v>-3160</v>
       </c>
-      <c r="C463" t="s">
-        <v>0</v>
-      </c>
-      <c r="D463">
+      <c r="C463">
         <v>-4024</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464">
         <v>463</v>
       </c>
       <c r="B464">
         <v>-3160</v>
       </c>
-      <c r="C464" t="s">
-        <v>0</v>
-      </c>
-      <c r="D464">
+      <c r="C464">
         <v>3368</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A465">
         <v>464</v>
       </c>
       <c r="B465">
         <v>-3176</v>
       </c>
-      <c r="C465" t="s">
-        <v>0</v>
-      </c>
-      <c r="D465">
+      <c r="C465">
         <v>-3800</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A466">
         <v>465</v>
       </c>
       <c r="B466">
         <v>-3352</v>
       </c>
-      <c r="C466" t="s">
-        <v>0</v>
-      </c>
-      <c r="D466">
+      <c r="C466">
         <v>-600</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A467">
         <v>466</v>
       </c>
       <c r="B467">
         <v>-3384</v>
       </c>
-      <c r="C467" t="s">
-        <v>0</v>
-      </c>
-      <c r="D467">
+      <c r="C467">
         <v>-3112</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A468">
         <v>467</v>
       </c>
       <c r="B468">
         <v>-3416</v>
       </c>
-      <c r="C468" t="s">
-        <v>0</v>
-      </c>
-      <c r="D468">
+      <c r="C468">
         <v>-3384</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A469">
         <v>468</v>
       </c>
       <c r="B469">
         <v>-3416</v>
       </c>
-      <c r="C469" t="s">
-        <v>0</v>
-      </c>
-      <c r="D469">
+      <c r="C469">
         <v>-3736</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A470">
         <v>469</v>
       </c>
       <c r="B470">
         <v>-3416</v>
       </c>
-      <c r="C470" t="s">
-        <v>0</v>
-      </c>
-      <c r="D470">
+      <c r="C470">
         <v>2584</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A471">
         <v>470</v>
       </c>
       <c r="B471">
         <v>-3416</v>
       </c>
-      <c r="C471" t="s">
-        <v>0</v>
-      </c>
-      <c r="D471">
+      <c r="C471">
         <v>3208</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A472">
         <v>471</v>
       </c>
       <c r="B472">
         <v>-3416</v>
       </c>
-      <c r="C472" t="s">
-        <v>0</v>
-      </c>
-      <c r="D472">
+      <c r="C472">
         <v>3640</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A473">
         <v>472</v>
       </c>
       <c r="B473">
         <v>-3448</v>
       </c>
-      <c r="C473" t="s">
-        <v>0</v>
-      </c>
-      <c r="D473">
+      <c r="C473">
         <v>-3976</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A474">
         <v>473</v>
       </c>
       <c r="B474">
         <v>-3464</v>
       </c>
-      <c r="C474" t="s">
-        <v>0</v>
-      </c>
-      <c r="D474">
+      <c r="C474">
         <v>-6040</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475">
         <v>474</v>
       </c>
       <c r="B475">
         <v>-3512</v>
       </c>
-      <c r="C475" t="s">
-        <v>0</v>
-      </c>
-      <c r="D475">
+      <c r="C475">
         <v>3880</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A476">
         <v>475</v>
       </c>
       <c r="B476">
         <v>-3688</v>
       </c>
-      <c r="C476" t="s">
-        <v>0</v>
-      </c>
-      <c r="D476">
+      <c r="C476">
         <v>-6008</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A477">
         <v>476</v>
       </c>
       <c r="B477">
         <v>-3688</v>
       </c>
-      <c r="C477" t="s">
-        <v>0</v>
-      </c>
-      <c r="D477">
+      <c r="C477">
         <v>-3496</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A478">
         <v>477</v>
       </c>
       <c r="B478">
         <v>-3688</v>
       </c>
-      <c r="C478" t="s">
-        <v>0</v>
-      </c>
-      <c r="D478">
+      <c r="C478">
         <v>3640</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A479">
         <v>478</v>
       </c>
       <c r="B479">
         <v>-3720</v>
       </c>
-      <c r="C479" t="s">
-        <v>0</v>
-      </c>
-      <c r="D479">
+      <c r="C479">
         <v>3384</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A480">
         <v>479</v>
       </c>
       <c r="B480">
         <v>-3800</v>
       </c>
-      <c r="C480" t="s">
-        <v>0</v>
-      </c>
-      <c r="D480">
+      <c r="C480">
         <v>-552</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A481">
         <v>480</v>
       </c>
       <c r="B481">
         <v>-3816</v>
       </c>
-      <c r="C481" t="s">
-        <v>0</v>
-      </c>
-      <c r="D481">
+      <c r="C481">
         <v>2952</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A482">
         <v>481</v>
       </c>
       <c r="B482">
         <v>-3992</v>
       </c>
-      <c r="C482" t="s">
-        <v>0</v>
-      </c>
-      <c r="D482">
+      <c r="C482">
         <v>-520</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A483">
         <v>482</v>
       </c>
       <c r="B483">
         <v>-3992</v>
       </c>
-      <c r="C483" t="s">
-        <v>0</v>
-      </c>
-      <c r="D483">
+      <c r="C483">
         <v>3240</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A484">
         <v>483</v>
       </c>
       <c r="B484">
         <v>-4008</v>
       </c>
-      <c r="C484" t="s">
-        <v>0</v>
-      </c>
-      <c r="D484">
+      <c r="C484">
         <v>-4456</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A485">
         <v>484</v>
       </c>
       <c r="B485">
         <v>-4024</v>
       </c>
-      <c r="C485" t="s">
-        <v>0</v>
-      </c>
-      <c r="D485">
+      <c r="C485">
         <v>-5336</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486">
         <v>485</v>
       </c>
       <c r="B486">
         <v>-4040</v>
       </c>
-      <c r="C486" t="s">
-        <v>0</v>
-      </c>
-      <c r="D486">
+      <c r="C486">
         <v>-5576</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A487">
         <v>486</v>
       </c>
       <c r="B487">
         <v>-4056</v>
       </c>
-      <c r="C487" t="s">
-        <v>0</v>
-      </c>
-      <c r="D487">
+      <c r="C487">
         <v>-4648</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A488">
         <v>487</v>
       </c>
       <c r="B488">
         <v>-4088</v>
       </c>
-      <c r="C488" t="s">
-        <v>0</v>
-      </c>
-      <c r="D488">
+      <c r="C488">
         <v>-4056</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A489">
         <v>488</v>
       </c>
       <c r="B489">
         <v>-4104</v>
       </c>
-      <c r="C489" t="s">
-        <v>0</v>
-      </c>
-      <c r="D489">
+      <c r="C489">
         <v>-840</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A490">
         <v>489</v>
       </c>
       <c r="B490">
         <v>-4152</v>
       </c>
-      <c r="C490" t="s">
-        <v>0</v>
-      </c>
-      <c r="D490">
+      <c r="C490">
         <v>-6040</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A491">
         <v>490</v>
       </c>
       <c r="B491">
         <v>-4296</v>
       </c>
-      <c r="C491" t="s">
-        <v>0</v>
-      </c>
-      <c r="D491">
+      <c r="C491">
         <v>-4328</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A492">
         <v>491</v>
       </c>
       <c r="B492">
         <v>-4312</v>
       </c>
-      <c r="C492" t="s">
-        <v>0</v>
-      </c>
-      <c r="D492">
+      <c r="C492">
         <v>-4648</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A493">
         <v>492</v>
       </c>
       <c r="B493">
         <v>-4312</v>
       </c>
-      <c r="C493" t="s">
-        <v>0</v>
-      </c>
-      <c r="D493">
+      <c r="C493">
         <v>-4120</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A494">
         <v>493</v>
       </c>
       <c r="B494">
         <v>-4328</v>
       </c>
-      <c r="C494" t="s">
-        <v>0</v>
-      </c>
-      <c r="D494">
+      <c r="C494">
         <v>-5896</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A495">
         <v>494</v>
       </c>
       <c r="B495">
         <v>-4392</v>
       </c>
-      <c r="C495" t="s">
-        <v>0</v>
-      </c>
-      <c r="D495">
+      <c r="C495">
         <v>-5720</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A496">
         <v>495</v>
       </c>
       <c r="B496">
         <v>-4392</v>
       </c>
-      <c r="C496" t="s">
-        <v>0</v>
-      </c>
-      <c r="D496">
+      <c r="C496">
         <v>-5048</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497">
         <v>496</v>
       </c>
       <c r="B497">
         <v>-4424</v>
       </c>
-      <c r="C497" t="s">
-        <v>0</v>
-      </c>
-      <c r="D497">
+      <c r="C497">
         <v>-5256</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A498">
         <v>497</v>
       </c>
       <c r="B498">
         <v>-4472</v>
       </c>
-      <c r="C498" t="s">
-        <v>0</v>
-      </c>
-      <c r="D498">
+      <c r="C498">
         <v>-1480</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A499">
         <v>498</v>
       </c>
       <c r="B499">
         <v>-4472</v>
       </c>
-      <c r="C499" t="s">
-        <v>0</v>
-      </c>
-      <c r="D499">
+      <c r="C499">
         <v>2344</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A500">
         <v>499</v>
       </c>
       <c r="B500">
         <v>-4472</v>
       </c>
-      <c r="C500" t="s">
-        <v>0</v>
-      </c>
-      <c r="D500">
+      <c r="C500">
         <v>2104</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A501">
         <v>500</v>
       </c>
       <c r="B501">
         <v>-4632</v>
       </c>
-      <c r="C501" t="s">
-        <v>0</v>
-      </c>
-      <c r="D501">
+      <c r="C501">
         <v>-5656</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A502">
         <v>501</v>
       </c>
       <c r="B502">
         <v>-4680</v>
       </c>
-      <c r="C502" t="s">
-        <v>0</v>
-      </c>
-      <c r="D502">
+      <c r="C502">
         <v>-4424</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A503">
         <v>502</v>
       </c>
       <c r="B503">
         <v>-4680</v>
       </c>
-      <c r="C503" t="s">
-        <v>0</v>
-      </c>
-      <c r="D503">
+      <c r="C503">
         <v>2264</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A504">
         <v>503</v>
       </c>
       <c r="B504">
         <v>-4696</v>
       </c>
-      <c r="C504" t="s">
-        <v>0</v>
-      </c>
-      <c r="D504">
+      <c r="C504">
         <v>-5912</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A505">
         <v>504</v>
       </c>
       <c r="B505">
         <v>-4696</v>
       </c>
-      <c r="C505" t="s">
-        <v>0</v>
-      </c>
-      <c r="D505">
+      <c r="C505">
         <v>-4680</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A506">
         <v>505</v>
       </c>
       <c r="B506">
         <v>-4728</v>
       </c>
-      <c r="C506" t="s">
-        <v>0</v>
-      </c>
-      <c r="D506">
+      <c r="C506">
         <v>-3752</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A507">
         <v>506</v>
       </c>
       <c r="B507">
         <v>-4760</v>
       </c>
-      <c r="C507" t="s">
-        <v>0</v>
-      </c>
-      <c r="D507">
+      <c r="C507">
         <v>-5288</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508">
         <v>507</v>
       </c>
       <c r="B508">
         <v>-4776</v>
       </c>
-      <c r="C508" t="s">
-        <v>0</v>
-      </c>
-      <c r="D508">
+      <c r="C508">
         <v>-4152</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A509">
         <v>508</v>
       </c>
       <c r="B509">
         <v>-4792</v>
       </c>
-      <c r="C509" t="s">
-        <v>0</v>
-      </c>
-      <c r="D509">
+      <c r="C509">
         <v>-5048</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A510">
         <v>509</v>
       </c>
       <c r="B510">
         <v>-4936</v>
       </c>
-      <c r="C510" t="s">
-        <v>0</v>
-      </c>
-      <c r="D510">
+      <c r="C510">
         <v>-472</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A511">
         <v>510</v>
       </c>
       <c r="B511">
         <v>-4984</v>
       </c>
-      <c r="C511" t="s">
-        <v>0</v>
-      </c>
-      <c r="D511">
+      <c r="C511">
         <v>-4328</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A512">
         <v>511</v>
       </c>
       <c r="B512">
         <v>-4984</v>
       </c>
-      <c r="C512" t="s">
-        <v>0</v>
-      </c>
-      <c r="D512">
+      <c r="C512">
         <v>5304</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A513">
         <v>512</v>
       </c>
       <c r="B513">
         <v>-5000</v>
       </c>
-      <c r="C513" t="s">
-        <v>0</v>
-      </c>
-      <c r="D513">
+      <c r="C513">
         <v>5848</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A514">
         <v>513</v>
       </c>
       <c r="B514">
         <v>-5016</v>
       </c>
-      <c r="C514" t="s">
-        <v>0</v>
-      </c>
-      <c r="D514">
+      <c r="C514">
         <v>-1464</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A515">
         <v>514</v>
       </c>
       <c r="B515">
         <v>-5032</v>
       </c>
-      <c r="C515" t="s">
-        <v>0</v>
-      </c>
-      <c r="D515">
+      <c r="C515">
         <v>-3768</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A516">
         <v>515</v>
       </c>
       <c r="B516">
         <v>-5048</v>
       </c>
-      <c r="C516" t="s">
-        <v>0</v>
-      </c>
-      <c r="D516">
+      <c r="C516">
         <v>-5416</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A517">
         <v>516</v>
       </c>
       <c r="B517">
         <v>-5064</v>
       </c>
-      <c r="C517" t="s">
-        <v>0</v>
-      </c>
-      <c r="D517">
+      <c r="C517">
         <v>728</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A518">
         <v>517</v>
       </c>
       <c r="B518">
         <v>-5096</v>
       </c>
-      <c r="C518" t="s">
-        <v>0</v>
-      </c>
-      <c r="D518">
+      <c r="C518">
         <v>-4152</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519">
         <v>518</v>
       </c>
       <c r="B519">
         <v>-5112</v>
       </c>
-      <c r="C519" t="s">
-        <v>0</v>
-      </c>
-      <c r="D519">
+      <c r="C519">
         <v>-4936</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A520">
         <v>519</v>
       </c>
       <c r="B520">
         <v>-5112</v>
       </c>
-      <c r="C520" t="s">
-        <v>0</v>
-      </c>
-      <c r="D520">
+      <c r="C520">
         <v>-1736</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A521">
         <v>520</v>
       </c>
       <c r="B521">
         <v>-5112</v>
       </c>
-      <c r="C521" t="s">
-        <v>0</v>
-      </c>
-      <c r="D521">
+      <c r="C521">
         <v>-1176</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A522">
         <v>521</v>
       </c>
       <c r="B522">
         <v>-5272</v>
       </c>
-      <c r="C522" t="s">
-        <v>0</v>
-      </c>
-      <c r="D522">
+      <c r="C522">
         <v>-1880</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A523">
         <v>522</v>
       </c>
       <c r="B523">
         <v>-5320</v>
       </c>
-      <c r="C523" t="s">
-        <v>0</v>
-      </c>
-      <c r="D523">
+      <c r="C523">
         <v>-5096</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A524">
         <v>523</v>
       </c>
       <c r="B524">
         <v>-5336</v>
       </c>
-      <c r="C524" t="s">
-        <v>0</v>
-      </c>
-      <c r="D524">
+      <c r="C524">
         <v>-1448</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A525">
         <v>524</v>
       </c>
       <c r="B525">
         <v>-5368</v>
       </c>
-      <c r="C525" t="s">
-        <v>0</v>
-      </c>
-      <c r="D525">
+      <c r="C525">
         <v>5880</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A526">
         <v>525</v>
       </c>
       <c r="B526">
         <v>-5368</v>
       </c>
-      <c r="C526" t="s">
-        <v>0</v>
-      </c>
-      <c r="D526">
+      <c r="C526">
         <v>5560</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A527">
         <v>526</v>
       </c>
       <c r="B527">
         <v>-5416</v>
       </c>
-      <c r="C527" t="s">
-        <v>0</v>
-      </c>
-      <c r="D527">
+      <c r="C527">
         <v>-2232</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A528">
         <v>527</v>
       </c>
       <c r="B528">
         <v>-5432</v>
       </c>
-      <c r="C528" t="s">
-        <v>0</v>
-      </c>
-      <c r="D528">
+      <c r="C528">
         <v>-1208</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A529">
         <v>528</v>
       </c>
       <c r="B529">
         <v>-5576</v>
       </c>
-      <c r="C529" t="s">
-        <v>0</v>
-      </c>
-      <c r="D529">
+      <c r="C529">
         <v>-5032</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530">
         <v>529</v>
       </c>
       <c r="B530">
         <v>-5640</v>
       </c>
-      <c r="C530" t="s">
-        <v>0</v>
-      </c>
-      <c r="D530">
+      <c r="C530">
         <v>-488</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A531">
         <v>530</v>
       </c>
       <c r="B531">
         <v>-5672</v>
       </c>
-      <c r="C531" t="s">
-        <v>0</v>
-      </c>
-      <c r="D531">
+      <c r="C531">
         <v>-3496</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A532">
         <v>531</v>
       </c>
       <c r="B532">
         <v>-5688</v>
       </c>
-      <c r="C532" t="s">
-        <v>0</v>
-      </c>
-      <c r="D532">
+      <c r="C532">
         <v>-2696</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A533">
         <v>532</v>
       </c>
       <c r="B533">
         <v>-5688</v>
       </c>
-      <c r="C533" t="s">
-        <v>0</v>
-      </c>
-      <c r="D533">
+      <c r="C533">
         <v>5944</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A534">
         <v>533</v>
       </c>
       <c r="B534">
         <v>-5704</v>
       </c>
-      <c r="C534" t="s">
-        <v>0</v>
-      </c>
-      <c r="D534">
+      <c r="C534">
         <v>-888</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A535">
         <v>534</v>
       </c>
       <c r="B535">
         <v>-5720</v>
       </c>
-      <c r="C535" t="s">
-        <v>0</v>
-      </c>
-      <c r="D535">
+      <c r="C535">
         <v>-2520</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A536">
         <v>535</v>
       </c>
       <c r="B536">
         <v>-5720</v>
       </c>
-      <c r="C536" t="s">
-        <v>0</v>
-      </c>
-      <c r="D536">
+      <c r="C536">
         <v>5608</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A537">
         <v>536</v>
       </c>
       <c r="B537">
         <v>-5896</v>
       </c>
-      <c r="C537" t="s">
-        <v>0</v>
-      </c>
-      <c r="D537">
+      <c r="C537">
         <v>-3400</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A538">
         <v>537</v>
       </c>
       <c r="B538">
         <v>-5928</v>
       </c>
-      <c r="C538" t="s">
-        <v>0</v>
-      </c>
-      <c r="D538">
+      <c r="C538">
         <v>-2088</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A539">
         <v>538</v>
       </c>
       <c r="B539">
         <v>-5976</v>
       </c>
-      <c r="C539" t="s">
-        <v>0</v>
-      </c>
-      <c r="D539">
+      <c r="C539">
         <v>-2488</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A540">
         <v>539</v>
       </c>
       <c r="B540">
         <v>-5992</v>
       </c>
-      <c r="C540" t="s">
-        <v>0</v>
-      </c>
-      <c r="D540">
+      <c r="C540">
         <v>1320</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541">
         <v>540</v>
       </c>
       <c r="B541">
         <v>-6040</v>
       </c>
-      <c r="C541" t="s">
-        <v>0</v>
-      </c>
-      <c r="D541">
+      <c r="C541">
         <v>-2808</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A542">
         <v>541</v>
       </c>
       <c r="B542">
         <v>-6040</v>
       </c>
-      <c r="C542" t="s">
-        <v>0</v>
-      </c>
-      <c r="D542">
+      <c r="C542">
         <v>-1192</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C1" xr:uid="{8D438CDC-9054-4E83-AD2E-7D63B2C25346}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C542">
+      <sortCondition descending="1" ref="B1:B542"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>